--- a/Recursos/Nuevo simulador Convenios 14.04.xlsx
+++ b/Recursos/Nuevo simulador Convenios 14.04.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NAYUF YUNIS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A365\Documents\Fuvex Banco de Crédito\Modelos\fuvex-manager-a365\Recursos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B2F54C-FA3D-4C2C-8F65-F37C4D862365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B54F275-6932-4A6B-A74F-C5AB97B58C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Chjb0x6aaVo9gpmP2c08EjJRxXdpTovIb6Z7fuwPwrjXbgx90w9mXIvrSmw/Flku+mf5XebhbALyTcvKDXun8w==" workbookSaltValue="XcFHcfXnrAv+TRCxRgnLfw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{14853C3E-07FD-4C4A-86F3-62F51240E739}"/>
@@ -494,9 +494,6 @@
     <t>Envío de estado de cuenta</t>
   </si>
   <si>
-    <t>Virtual</t>
-  </si>
-  <si>
     <t>i</t>
   </si>
   <si>
@@ -726,6 +723,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Físico</t>
   </si>
 </sst>
 </file>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M4">
         <f>IF(AND(Cáratula!$G$9=A4,DAY(Cáratula!$G$37)&lt;H4),2,IF(AND(Cáratula!$G$9=A4,DAY(Cáratula!$G$37))&gt;=H4,1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -3594,7 +3594,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A7"/>
       <c r="B7" s="3" t="s">
         <v>116</v>
@@ -3693,7 +3693,7 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13" s="52" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
@@ -3737,7 +3737,7 @@
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="51">
-        <v>3927.23</v>
+        <v>2500</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
@@ -3751,7 +3751,9 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="51"/>
+      <c r="G16" s="51">
+        <v>250</v>
+      </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="L16" s="25"/>
@@ -3765,7 +3767,9 @@
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="51"/>
+      <c r="G17" s="51">
+        <v>250</v>
+      </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" s="25"/>
@@ -3783,7 +3787,9 @@
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
-      <c r="G18" s="51"/>
+      <c r="G18" s="51">
+        <v>500</v>
+      </c>
       <c r="H18"/>
       <c r="I18"/>
     </row>
@@ -3820,7 +3826,9 @@
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
-      <c r="G21" s="28"/>
+      <c r="G21" s="28">
+        <v>200</v>
+      </c>
       <c r="H21"/>
       <c r="I21"/>
     </row>
@@ -3858,7 +3866,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="28">
-        <v>183.88</v>
+        <v>400</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
@@ -3885,7 +3893,7 @@
       <c r="F26" s="19"/>
       <c r="G26" s="20">
         <f>IF(G9="U_San_Juan_Bautista",G15*J11,((G15-G16+(G17*0.5)+G18-G21-G24)*L13))</f>
-        <v>1684.5074999999999</v>
+        <v>1023.75</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
@@ -3927,7 +3935,7 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="28">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
@@ -3954,13 +3962,13 @@
       <c r="F31" s="8"/>
       <c r="G31" s="17">
         <f>IF(G15=0,"",K31)</f>
-        <v>1645.5074999999999</v>
+        <v>1023.75</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="K31" s="21">
         <f>IF(G9="Ejercito_del_Perú",G26-G28-G29-5,G26-G28-G29)</f>
-        <v>1645.5074999999999</v>
+        <v>1023.75</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -3995,7 +4003,7 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" s="30">
-        <v>83500</v>
+        <v>25000</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
@@ -4010,7 +4018,7 @@
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35" s="31">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
@@ -4040,7 +4048,7 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37" s="32">
-        <v>46129</v>
+        <v>46147</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
@@ -4056,7 +4064,7 @@
       <c r="F38"/>
       <c r="G38" s="13">
         <f>DATE(YEAR(EDATE(G37,D70)),MONTH(EDATE(G37,D70)),D69)</f>
-        <v>46218</v>
+        <v>46249</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
@@ -4101,12 +4109,12 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40" s="34" t="s">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K40" s="26">
         <f>K39/365</f>
@@ -4114,7 +4122,7 @@
       </c>
       <c r="L40" s="26"/>
       <c r="O40" s="57" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P40" s="100">
         <f>P39/365</f>
@@ -4124,19 +4132,19 @@
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41"/>
       <c r="B41" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41" s="44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K41" s="23">
         <f>K40*31</f>
@@ -4144,7 +4152,7 @@
       </c>
       <c r="L41" s="23"/>
       <c r="O41" s="57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P41" s="99">
         <f>P40*31</f>
@@ -4159,7 +4167,7 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
@@ -4170,7 +4178,7 @@
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43"/>
       <c r="B43" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C43"/>
       <c r="D43"/>
@@ -4186,7 +4194,7 @@
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44"/>
       <c r="B44" s="105" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C44"/>
       <c r="D44"/>
@@ -4194,7 +4202,7 @@
       <c r="F44"/>
       <c r="G44" s="104">
         <f>VLOOKUP(G9,Base!$A$1:$M$20,13,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
@@ -4213,7 +4221,7 @@
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46"/>
       <c r="B46" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46"/>
       <c r="D46"/>
@@ -4223,7 +4231,7 @@
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K46" s="21">
         <v>0</v>
@@ -4251,19 +4259,19 @@
       <c r="H48"/>
       <c r="I48"/>
       <c r="P48" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q48" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="Q48" s="57" t="s">
+      <c r="R48" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="R48" s="57" t="s">
+      <c r="S48" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="S48" s="57" t="s">
+      <c r="T48" s="57" t="s">
         <v>155</v>
-      </c>
-      <c r="T48" s="57" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:24" ht="5.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -4282,30 +4290,30 @@
       <c r="B50" s="46"/>
       <c r="C50" s="45"/>
       <c r="D50" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="E50" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="E50" s="47" t="s">
+      <c r="F50" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="F50" s="47" t="s">
+      <c r="G50" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="G50" s="47" t="s">
+      <c r="H50" s="56" t="s">
         <v>160</v>
-      </c>
-      <c r="H50" s="56" t="s">
-        <v>161</v>
       </c>
       <c r="I50" s="55"/>
       <c r="J50" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K50" s="49">
         <v>7.67E-4</v>
       </c>
       <c r="L50" s="49"/>
       <c r="O50" s="58" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P50" s="58">
         <v>3.3060000000000003E-3</v>
@@ -4326,7 +4334,7 @@
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51"/>
       <c r="B51" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C51"/>
       <c r="D51" s="40"/>
@@ -4339,7 +4347,7 @@
       </c>
       <c r="I51" s="20"/>
       <c r="J51" s="21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K51" s="42">
         <v>9.9700000000000006E-4</v>
@@ -4354,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P51" s="57">
         <v>5.306E-3</v>
@@ -4372,13 +4380,13 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="X51" s="57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52"/>
       <c r="B52" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C52"/>
       <c r="D52" s="30"/>
@@ -4399,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P52" s="57">
         <v>6.5829999999999994E-3</v>
@@ -4417,7 +4425,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="W52" s="58" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X52" s="58">
         <v>3.5000000000000003E-2</v>
@@ -4426,7 +4434,7 @@
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53"/>
       <c r="B53" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C53"/>
       <c r="D53" s="30"/>
@@ -4451,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P53" s="57">
         <v>7.1390000000000004E-3</v>
@@ -4469,7 +4477,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="W53" s="57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X53" s="57">
         <v>3.6999999999999998E-2</v>
@@ -4478,7 +4486,7 @@
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54"/>
       <c r="B54" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C54"/>
       <c r="D54" s="30"/>
@@ -4499,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="103" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P54" s="103">
         <v>7.417E-3</v>
@@ -4517,7 +4525,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="W54" s="57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X54" s="57">
         <v>3.9E-2</v>
@@ -4526,7 +4534,7 @@
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55"/>
       <c r="B55" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C55"/>
       <c r="D55" s="30"/>
@@ -4547,7 +4555,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P55" s="57">
         <v>7.417E-3</v>
@@ -4565,7 +4573,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="W55" s="57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X55" s="57">
         <v>4.1000000000000002E-2</v>
@@ -4574,7 +4582,7 @@
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56"/>
       <c r="B56" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C56"/>
       <c r="D56" s="30"/>
@@ -4595,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="X56" s="57">
         <v>4.3999999999999997E-2</v>
@@ -4604,36 +4612,34 @@
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57"/>
       <c r="B57" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30">
-        <v>5</v>
-      </c>
-      <c r="F57" s="30">
-        <v>65</v>
-      </c>
+      <c r="D57" s="30">
+        <v>600</v>
+      </c>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
       <c r="G57" s="30"/>
       <c r="H57" s="20">
         <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",G57&lt;&gt;""),L57,N57)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I57" s="20"/>
       <c r="K57" s="21">
         <f>((G51/100)+(G53*0.035)+(G54*0.022)+(G56*0.0006944)+(G57*0.078)+(G58*0.003306)+E51+E52+E53+E56+E57+E58+D51+D52+D53+D54+D55+E55+D56+E54+D57+D58)/(G15-G21+G18-G24-G29)</f>
-        <v>9.718304155924791E-3</v>
-      </c>
-      <c r="L57" s="25">
+        <v>0.25</v>
+      </c>
+      <c r="L57" s="25" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N57" s="59">
         <f>IF(E57="",G57*(P54),E57)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W57" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X57" s="57">
         <v>4.3999999999999997E-2</v>
@@ -4642,40 +4648,36 @@
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58"/>
       <c r="B58" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C58"/>
       <c r="D58" s="30"/>
-      <c r="E58" s="30">
-        <v>31</v>
-      </c>
-      <c r="F58" s="30">
-        <v>8435</v>
-      </c>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
       <c r="G58" s="30"/>
       <c r="H58" s="20">
         <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",G58&lt;&gt;""),L58,N58)</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I58" s="20"/>
       <c r="J58" s="21">
         <f>P54</f>
         <v>7.417E-3</v>
       </c>
-      <c r="L58" s="25">
+      <c r="L58" s="25" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N58" s="59">
         <f>IF(E58="",G58*J58,E58)</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="X58" s="57"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59"/>
       <c r="B59" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59"/>
       <c r="D59"/>
@@ -4683,7 +4685,7 @@
       <c r="F59" s="38"/>
       <c r="G59" s="41">
         <f>IF(K57=0,"",K57)</f>
-        <v>9.718304155924791E-3</v>
+        <v>0.25</v>
       </c>
       <c r="H59"/>
       <c r="I59"/>
@@ -4691,7 +4693,7 @@
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60"/>
       <c r="B60" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C60"/>
       <c r="D60"/>
@@ -4699,7 +4701,7 @@
       <c r="F60" s="38"/>
       <c r="G60" s="50">
         <f>((G15-G16+G17+G18-G21-G24-G29)*K60)-D51-D52-D53-D54-D55-D56-D57-D58-N51-N52-N53-N54-N55-N56-N57-N58</f>
-        <v>2371.8274999999999</v>
+        <v>960</v>
       </c>
       <c r="H60"/>
       <c r="I60"/>
@@ -4715,7 +4717,7 @@
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61"/>
       <c r="B61" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C61"/>
       <c r="D61"/>
@@ -4742,7 +4744,7 @@
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63"/>
       <c r="B63" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C63"/>
       <c r="D63"/>
@@ -4752,24 +4754,24 @@
       <c r="H63"/>
       <c r="I63"/>
       <c r="J63" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K63" s="21">
         <f>((K41+P41)/(1-(1+K41+P41)^(-G35)))</f>
-        <v>1.9425381519096178E-2</v>
+        <v>4.6961265439388396E-2</v>
       </c>
       <c r="O63" s="57" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P63" s="101">
         <f>G34*POWER(1+K41+P41,D68)</f>
-        <v>85144.557062224907</v>
+        <v>25492.382353959554</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64"/>
       <c r="B64" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C64"/>
       <c r="D64"/>
@@ -4782,7 +4784,7 @@
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65"/>
       <c r="B65" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C65"/>
       <c r="D65"/>
@@ -4792,18 +4794,18 @@
       <c r="H65"/>
       <c r="I65"/>
       <c r="J65" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K65" s="21">
         <f>IF(Cronograma!C20="",(Cronograma!F23+Cronograma!J21+Cronograma!J22)*K63,(Cronograma!G23+Cronograma!J20+Cronograma!J21+Cronograma!J22)*K63)</f>
-        <v>1640.3277390434066</v>
+        <v>1198.890417110621</v>
       </c>
       <c r="O65" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P65" s="102">
         <f>-PMT(K41+P41,G35,P63)</f>
-        <v>1653.9655052081757</v>
+        <v>1197.1545344066778</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
@@ -4831,7 +4833,7 @@
     <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68"/>
       <c r="B68" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C68" s="15"/>
       <c r="D68" s="16">
@@ -4844,18 +4846,18 @@
       <c r="H68"/>
       <c r="I68"/>
       <c r="J68" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K68" s="27">
         <f>IRR(Cronograma!P20:P94,2%)</f>
-        <v>1.0227656199806479E-2</v>
+        <v>1.2550801109184606E-2</v>
       </c>
       <c r="L68" s="27"/>
     </row>
     <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69"/>
       <c r="B69" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="16">
@@ -4868,18 +4870,18 @@
       <c r="H69"/>
       <c r="I69"/>
       <c r="J69" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K69" s="27">
         <f>(1+K68)^12-1</f>
-        <v>0.12987667724061969</v>
+        <v>0.16145358607522109</v>
       </c>
       <c r="L69" s="27"/>
     </row>
     <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70"/>
       <c r="B70" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C70" s="15"/>
       <c r="D70" s="16">
@@ -4993,7 +4995,7 @@
     <row r="7" spans="2:16" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="64"/>
       <c r="C7" s="64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
@@ -5011,7 +5013,7 @@
     </row>
     <row r="8" spans="2:16" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="107" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" s="107"/>
       <c r="D8" s="107"/>
@@ -5038,7 +5040,7 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C10" s="69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D10" s="69"/>
       <c r="E10" s="69"/>
@@ -5056,7 +5058,7 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C11" s="69" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D11" s="69"/>
       <c r="E11" s="69"/>
@@ -5067,7 +5069,7 @@
       <c r="J11" s="71"/>
       <c r="K11" s="70">
         <f>IF(Cáratula!K69="","",Cáratula!K69)</f>
-        <v>0.12987667724061969</v>
+        <v>0.16145358607522109</v>
       </c>
       <c r="O11" s="61"/>
       <c r="P11" s="61"/>
@@ -5078,7 +5080,7 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C13" s="72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D13" s="72"/>
       <c r="E13" s="72"/>
@@ -5089,33 +5091,33 @@
     <row r="15" spans="2:16" x14ac:dyDescent="0.3"/>
     <row r="16" spans="2:16" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I16" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="J16" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="J16" s="73" t="s">
+      <c r="K16" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="K16" s="73" t="s">
+      <c r="L16" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="M16" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="L16" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="M16" s="73" t="s">
+      <c r="N16" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="N16" s="73" t="s">
+      <c r="O16" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="O16" s="73" t="s">
-        <v>202</v>
-      </c>
       <c r="P16" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B17" s="106" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="106"/>
       <c r="D17" s="106"/>
@@ -5125,23 +5127,23 @@
       <c r="H17" s="74"/>
       <c r="I17" s="75">
         <f t="shared" ref="I17:O17" si="0">SUM(I20:I1048576)</f>
-        <v>32600.651472348818</v>
+        <v>3512.4613582161051</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="0"/>
-        <v>2766.9992572858837</v>
+        <v>298.35728585630761</v>
       </c>
       <c r="K17" s="75">
         <f t="shared" si="0"/>
-        <v>83763.028306412452</v>
+        <v>25382.571413864316</v>
       </c>
       <c r="L17" s="75">
         <f t="shared" si="0"/>
-        <v>118391.59721112536</v>
+        <v>28869.370010654915</v>
       </c>
       <c r="M17" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N17" s="75">
         <f t="shared" si="0"/>
@@ -5153,87 +5155,87 @@
       </c>
       <c r="P17" s="75">
         <f>SUM(P21:P1048576)</f>
-        <v>118391.59721112536</v>
+        <v>29109.370010654915</v>
       </c>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:23" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B19" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="73" t="s">
+      <c r="D19" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="E19" s="73" t="s">
         <v>206</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="F19" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="G19" s="73" t="s">
         <v>208</v>
       </c>
-      <c r="G19" s="73" t="s">
+      <c r="H19" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="H19" s="73" t="s">
-        <v>210</v>
-      </c>
       <c r="I19" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="J19" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="J19" s="73" t="s">
+      <c r="K19" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="K19" s="73" t="s">
+      <c r="L19" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="M19" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="L19" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="M19" s="73" t="s">
+      <c r="N19" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="N19" s="73" t="s">
+      <c r="O19" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="O19" s="73" t="s">
-        <v>202</v>
-      </c>
       <c r="P19" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B20" s="76"/>
-      <c r="C20" s="77" t="str">
+      <c r="C20" s="77">
         <f>IF(DAY(Cáratula!G37)&gt;=Cáratula!D69,"",(IF(Cáratula!D68=2,(EDATE(C21,-1)),"")))</f>
-        <v/>
-      </c>
-      <c r="D20" s="76" t="str">
+        <v>46157</v>
+      </c>
+      <c r="D20" s="76">
         <f>IF(C20="","",(C20-Cáratula!G37))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="E20" s="76"/>
-      <c r="F20" s="78" t="str">
+      <c r="F20" s="78">
         <f>IF(C20="","",(IF(Cáratula!D68=2,Cáratula!G34,"")))</f>
-        <v/>
-      </c>
-      <c r="G20" s="79" t="str">
+        <v>25000</v>
+      </c>
+      <c r="G20" s="79">
         <f>IF(F20="","",F20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="80" t="str">
+        <v>25000</v>
+      </c>
+      <c r="H20" s="80">
         <f>IF(G20="","",(Cáratula!K39/365*D20))</f>
-        <v/>
-      </c>
-      <c r="I20" s="81" t="str">
+        <v>2.9090068094318093E-3</v>
+      </c>
+      <c r="I20" s="81">
         <f>IF(H20="","",(H20*F20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="82" t="str">
+        <v>72.725170235795233</v>
+      </c>
+      <c r="J20" s="82">
         <f>IF(C20="","",G20*Cáratula!P40*D20)</f>
-        <v/>
+        <v>6.3041095890410954</v>
       </c>
       <c r="K20" s="82"/>
       <c r="L20" s="82"/>
@@ -5242,42 +5244,42 @@
       <c r="O20" s="76"/>
       <c r="P20" s="83">
         <f>-Cáratula!G34</f>
-        <v>-83500</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="21" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B21" s="84"/>
       <c r="C21" s="85">
         <f>EDATE(C22,-1)</f>
-        <v>46157</v>
+        <v>46188</v>
       </c>
       <c r="D21" s="84">
         <f>C21-Cáratula!G37</f>
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E21" s="84">
         <f>IF(C20="",(C21-Cáratula!G37),(C21-C20))</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F21" s="86">
         <f>IF(F20="",Cáratula!G34,G20)</f>
-        <v>83500</v>
+        <v>25000</v>
       </c>
       <c r="G21" s="86">
         <f>IF(C20="",F21,G20)</f>
-        <v>83500</v>
+        <v>25000</v>
       </c>
       <c r="H21" s="87">
         <f>Cáratula!$K$39/365*E21</f>
-        <v>8.1452190664090662E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I21" s="86">
         <f>H21*F21</f>
-        <v>680.12579204515703</v>
+        <v>225.44802773096524</v>
       </c>
       <c r="J21" s="88">
         <f>IF(C20="",F21*E21*Cáratula!$P$40,Cáratula!P40*E21*G20)</f>
-        <v>58.956032876712328</v>
+        <v>19.542739726027396</v>
       </c>
       <c r="K21" s="88"/>
       <c r="L21" s="88"/>
@@ -5290,46 +5292,46 @@
       <c r="B22" s="76"/>
       <c r="C22" s="77">
         <f>EDATE(C23,-1)</f>
-        <v>46188</v>
+        <v>46218</v>
       </c>
       <c r="D22" s="76">
         <f>C22-Cáratula!G37</f>
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E22" s="76">
         <f>C22-C21</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F22" s="79">
         <f>IF(C20="",G21,G22)</f>
-        <v>83500</v>
+        <v>25244.990767456995</v>
       </c>
       <c r="G22" s="79">
         <f>IF(C20="",G21+I22+J22,G21+I21+J21)</f>
-        <v>84318.269163306351</v>
+        <v>25244.990767456995</v>
       </c>
       <c r="H22" s="80">
         <f>IF(OR($B23=""),$B23,(Cáratula!$K$39/365*E22))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I22" s="79">
         <f>IF(OR($B23=""),$B23,(H22*F22))</f>
-        <v>752.99641262142393</v>
+        <v>220.31355013972669</v>
       </c>
       <c r="J22" s="82">
         <f>IF(C20="",Cáratula!$P$40*E22*G21,Cáratula!P40*E22*G22)</f>
-        <v>65.272750684931509</v>
+        <v>19.097662604685549</v>
       </c>
       <c r="K22" s="89">
         <f>IF(OR($B23=""),$B23,(L22-I22-J22))</f>
-        <v>-818.26916330635549</v>
+        <v>-239.41121274441224</v>
       </c>
       <c r="L22" s="82"/>
       <c r="M22" s="82"/>
       <c r="N22" s="76"/>
       <c r="O22" s="76"/>
       <c r="P22" s="90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.3">
@@ -5338,7 +5340,7 @@
       </c>
       <c r="C23" s="85">
         <f>Cáratula!G38</f>
-        <v>46218</v>
+        <v>46249</v>
       </c>
       <c r="D23" s="84">
         <f>IF(OR($B24=""),"",$C23-Cáratula!$G$38)</f>
@@ -5346,45 +5348,45 @@
       </c>
       <c r="E23" s="84">
         <f t="shared" ref="E23:E54" si="1">IF(OR($B24=""),"",C23-C22)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F23" s="86">
         <f>G22</f>
-        <v>84318.269163306351</v>
+        <v>25244.990767456995</v>
       </c>
       <c r="G23" s="86">
         <f>IF(C20="",G22,G22+I22+J22)</f>
-        <v>84318.269163306351</v>
+        <v>25484.401980201408</v>
       </c>
       <c r="H23" s="87">
         <f>IF(OR($B24=""),$B24,(Cáratula!$K$39/365*E23))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I23" s="86">
         <f>IF(C20="",((H23*F23)+I21),((H23*F23)+I20))</f>
-        <v>1415.9730495118442</v>
+        <v>300.38250538017945</v>
       </c>
       <c r="J23" s="88">
         <f>IF(OR($B24=""),"",IF(C21="",Cáratula!$P$40*E23*G22,Cáratula!P40*E23*G23))</f>
-        <v>63.786193099649722</v>
+        <v>19.921401398901331</v>
       </c>
       <c r="K23" s="88">
         <f>L23-I23-J23</f>
-        <v>164.56849643191265</v>
+        <v>882.58651033154013</v>
       </c>
       <c r="L23" s="88">
         <f>Cáratula!K65+$W$24</f>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M23" s="88">
         <f>IF(OR($B24=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N23" s="84"/>
       <c r="O23" s="84"/>
       <c r="P23" s="88">
         <f>IF(OR($B24=""),"",O23+N23+M23+L23)</f>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.3">
@@ -5394,7 +5396,7 @@
       </c>
       <c r="C24" s="77">
         <f>IF(OR($B25=""),$B25,IF(DAY(EOMONTH($C23,1))&lt;Cáratula!$D$69,EOMONTH($C23,1),DATE(YEAR(EOMONTH($C23,1)),MONTH(EOMONTH($C23,1)),Cáratula!$D$69)))</f>
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D24" s="76">
         <f>IF(OR($B25=""),"",$C24-Cáratula!$G$38)</f>
@@ -5406,11 +5408,11 @@
       </c>
       <c r="F24" s="79">
         <f t="shared" ref="F24:F47" si="2">IF(OR($B25=""),"",G23)</f>
-        <v>84318.269163306351</v>
+        <v>25484.401980201408</v>
       </c>
       <c r="G24" s="79">
         <f>IF(OR($B25=""),"",F24-K23)</f>
-        <v>84153.700666874443</v>
+        <v>24601.815469869867</v>
       </c>
       <c r="H24" s="80">
         <f>IF(OR($B25=""),$B25,(Cáratula!$K$39/365*E24))</f>
@@ -5418,29 +5420,29 @@
       </c>
       <c r="I24" s="79">
         <f>IF(OR($B25=""),$B25,(H24*G24))</f>
-        <v>758.89143366435428</v>
+        <v>221.85723105133246</v>
       </c>
       <c r="J24" s="82">
         <f>IF(OR($B25=""),"",IF(C22="",Cáratula!$P$40*E24*G23,Cáratula!$P$40*E24*G24))</f>
-        <v>65.783754764589816</v>
+        <v>19.231475060616848</v>
       </c>
       <c r="K24" s="82">
         <f>IF(OR($B25=""),"",L24-I24-J24)</f>
-        <v>819.65255061446248</v>
+        <v>961.80171099867164</v>
       </c>
       <c r="L24" s="82">
         <f>IF(OR($B25=""),"",L23)</f>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M24" s="82">
         <f>M23</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N24" s="76"/>
       <c r="O24" s="76"/>
       <c r="P24" s="82">
         <f>O24+N24+M24+L24</f>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
       <c r="W24" s="8">
         <v>4</v>
@@ -5453,53 +5455,53 @@
       </c>
       <c r="C25" s="85">
         <f>IF(OR($B26=""),$B26,IF(DAY(EOMONTH($C24,1))&lt;Cáratula!$D$69,EOMONTH($C24,1),DATE(YEAR(EOMONTH($C24,1)),MONTH(EOMONTH($C24,1)),Cáratula!$D$69)))</f>
-        <v>46280</v>
+        <v>46310</v>
       </c>
       <c r="D25" s="84">
         <f>IF(OR($B26=""),"",$C25-Cáratula!$G$38)</f>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E25" s="84">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" s="86">
         <f t="shared" si="2"/>
-        <v>84153.700666874443</v>
+        <v>24601.815469869867</v>
       </c>
       <c r="G25" s="86">
         <f t="shared" ref="G25:G88" si="3">IF(OR($B26=""),"",F25-K24)</f>
-        <v>83334.048116259975</v>
+        <v>23640.013758871195</v>
       </c>
       <c r="H25" s="87">
         <f>IF(OR($B26=""),$B26,(Cáratula!$K$39/365*E25))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I25" s="86">
         <f t="shared" ref="I25:I88" si="4">IF(OR($B26=""),$B26,(H25*G25))</f>
-        <v>751.49987162592686</v>
+        <v>206.30688299885392</v>
       </c>
       <c r="J25" s="88">
         <f>IF(OR($B26=""),"",IF(C23="",Cáratula!$P$40*E25*G24,Cáratula!$P$40*E25*G25))</f>
-        <v>65.143024506092488</v>
+        <v>17.883508490683599</v>
       </c>
       <c r="K25" s="88">
         <f t="shared" ref="K25:K88" si="5">IF(OR($B26=""),"",L25-I25-J25)</f>
-        <v>827.68484291138725</v>
+        <v>978.70002562108346</v>
       </c>
       <c r="L25" s="88">
         <f t="shared" ref="L25:L90" si="6">IF(OR($B26=""),"",L24)</f>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M25" s="88">
         <f>IF(OR($B26=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N25" s="84"/>
       <c r="O25" s="84"/>
       <c r="P25" s="88">
         <f>IF(OR($B26=""),"",O25+N25+M25+L25)</f>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.3">
@@ -5509,7 +5511,7 @@
       </c>
       <c r="C26" s="77">
         <f>IF(OR($B27=""),$B27,IF(DAY(EOMONTH($C25,1))&lt;Cáratula!$D$69,EOMONTH($C25,1),DATE(YEAR(EOMONTH($C25,1)),MONTH(EOMONTH($C25,1)),Cáratula!$D$69)))</f>
-        <v>46310</v>
+        <v>46341</v>
       </c>
       <c r="D26" s="76">
         <f>IF(OR($B27=""),"",$C26-Cáratula!$G$38)</f>
@@ -5517,45 +5519,45 @@
       </c>
       <c r="E26" s="76">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F26" s="79">
         <f t="shared" si="2"/>
-        <v>83334.048116259975</v>
+        <v>23640.013758871195</v>
       </c>
       <c r="G26" s="79">
         <f t="shared" si="3"/>
-        <v>82506.363273348587</v>
+        <v>22661.31373325011</v>
       </c>
       <c r="H26" s="80">
         <f>IF(OR($B27=""),$B27,(Cáratula!$K$39/365*E26))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I26" s="79">
         <f t="shared" si="4"/>
-        <v>720.03471775087678</v>
+        <v>204.35793947815498</v>
       </c>
       <c r="J26" s="82">
         <f>IF(OR($B27=""),"",IF(C24="",Cáratula!$P$40*E26*G25,Cáratula!$P$40*E26*G26))</f>
-        <v>62.415498704210989</v>
+        <v>17.714566245550284</v>
       </c>
       <c r="K26" s="82">
         <f t="shared" si="5"/>
-        <v>861.87752258831881</v>
+        <v>980.81791138691574</v>
       </c>
       <c r="L26" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M26" s="82">
         <f>IF(OR($B27=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N26" s="76"/>
       <c r="O26" s="76"/>
       <c r="P26" s="82">
         <f>IF(OR($B27=""),"",O26+N26+M26+L26)</f>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="27" spans="2:23" x14ac:dyDescent="0.3">
@@ -5565,53 +5567,53 @@
       </c>
       <c r="C27" s="85">
         <f>IF(OR($B28=""),$B28,IF(DAY(EOMONTH($C26,1))&lt;Cáratula!$D$69,EOMONTH($C26,1),DATE(YEAR(EOMONTH($C26,1)),MONTH(EOMONTH($C26,1)),Cáratula!$D$69)))</f>
-        <v>46341</v>
+        <v>46371</v>
       </c>
       <c r="D27" s="84">
         <f>IF(OR($B28=""),"",$C27-Cáratula!$G$38)</f>
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27" s="84">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F27" s="86">
         <f t="shared" si="2"/>
-        <v>82506.363273348587</v>
+        <v>22661.31373325011</v>
       </c>
       <c r="G27" s="86">
         <f t="shared" si="3"/>
-        <v>81644.485750760272</v>
+        <v>21680.495821863195</v>
       </c>
       <c r="H27" s="87">
         <f>IF(OR($B28=""),$B28,(Cáratula!$K$39/365*E27))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I27" s="86">
         <f t="shared" si="4"/>
-        <v>736.26353150471186</v>
+        <v>189.20612993297379</v>
       </c>
       <c r="J27" s="88">
         <f>IF(OR($B28=""),"",IF(C25="",Cáratula!$P$40*E27*G26,Cáratula!$P$40*E27*G27))</f>
-        <v>63.822277403698422</v>
+        <v>16.401146592692779</v>
       </c>
       <c r="K27" s="88">
         <f t="shared" si="5"/>
-        <v>844.24193013499632</v>
+        <v>997.28314058495448</v>
       </c>
       <c r="L27" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M27" s="88">
         <f>IF(OR($B28=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N27" s="84"/>
       <c r="O27" s="84"/>
       <c r="P27" s="88">
         <f>IF(OR($B28=""),"",O27+N27+M27+L27)</f>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.3">
@@ -5621,7 +5623,7 @@
       </c>
       <c r="C28" s="77">
         <f>IF(OR($B29=""),$B29,IF(DAY(EOMONTH($C27,1))&lt;Cáratula!$D$69,EOMONTH($C27,1),DATE(YEAR(EOMONTH($C27,1)),MONTH(EOMONTH($C27,1)),Cáratula!$D$69)))</f>
-        <v>46371</v>
+        <v>46402</v>
       </c>
       <c r="D28" s="76">
         <f>IF(OR($B29=""),"",$C28-Cáratula!$G$38)</f>
@@ -5629,45 +5631,45 @@
       </c>
       <c r="E28" s="76">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28" s="79">
         <f t="shared" si="2"/>
-        <v>81644.485750760272</v>
+        <v>21680.495821863195</v>
       </c>
       <c r="G28" s="79">
         <f t="shared" si="3"/>
-        <v>80800.24382062527</v>
+        <v>20683.212681278241</v>
       </c>
       <c r="H28" s="80">
         <f>IF(OR($B29=""),$B29,(Cáratula!$K$39/365*E28))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I28" s="79">
         <f t="shared" si="4"/>
-        <v>705.14537843384824</v>
+        <v>186.51958024537075</v>
       </c>
       <c r="J28" s="82">
         <f>IF(OR($B29=""),"",IF(C26="",Cáratula!$P$40*E28*G27,Cáratula!$P$40*E28*G28))</f>
-        <v>61.124831023975474</v>
+        <v>16.168265685131598</v>
       </c>
       <c r="K28" s="82">
         <f t="shared" si="5"/>
-        <v>878.05752958558287</v>
+        <v>1000.2025711801186</v>
       </c>
       <c r="L28" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M28" s="82">
         <f>IF(OR($B29=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N28" s="76"/>
       <c r="O28" s="76"/>
       <c r="P28" s="82">
         <f t="shared" ref="P28:P91" si="7">IF(OR($B29=""),"",O28+N28+M28+L28)</f>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.3">
@@ -5677,7 +5679,7 @@
       </c>
       <c r="C29" s="85">
         <f>IF(OR($B30=""),$B30,IF(DAY(EOMONTH($C28,1))&lt;Cáratula!$D$69,EOMONTH($C28,1),DATE(YEAR(EOMONTH($C28,1)),MONTH(EOMONTH($C28,1)),Cáratula!$D$69)))</f>
-        <v>46402</v>
+        <v>46433</v>
       </c>
       <c r="D29" s="84">
         <f>IF(OR($B30=""),"",$C29-Cáratula!$G$38)</f>
@@ -5689,11 +5691,11 @@
       </c>
       <c r="F29" s="86">
         <f t="shared" si="2"/>
-        <v>80800.24382062527</v>
+        <v>20683.212681278241</v>
       </c>
       <c r="G29" s="86">
         <f t="shared" si="3"/>
-        <v>79922.186291039689</v>
+        <v>19683.010110098123</v>
       </c>
       <c r="H29" s="87">
         <f>IF(OR($B30=""),$B30,(Cáratula!$K$39/365*E29))</f>
@@ -5701,29 +5703,29 @@
       </c>
       <c r="I29" s="86">
         <f t="shared" si="4"/>
-        <v>720.73197085046741</v>
+        <v>177.49983236521084</v>
       </c>
       <c r="J29" s="88">
         <f>IF(OR($B30=""),"",IF(C27="",Cáratula!$P$40*E29*G28,Cáratula!$P$40*E29*G29))</f>
-        <v>62.475939400834541</v>
+        <v>15.386397744256538</v>
       </c>
       <c r="K29" s="88">
         <f t="shared" si="5"/>
-        <v>861.11982879210461</v>
+        <v>1010.0041870011537</v>
       </c>
       <c r="L29" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M29" s="88">
         <f>IF(OR($B30=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N29" s="84"/>
       <c r="O29" s="84"/>
       <c r="P29" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
@@ -5733,53 +5735,53 @@
       </c>
       <c r="C30" s="77">
         <f>IF(OR($B31=""),$B31,IF(DAY(EOMONTH($C29,1))&lt;Cáratula!$D$69,EOMONTH($C29,1),DATE(YEAR(EOMONTH($C29,1)),MONTH(EOMONTH($C29,1)),Cáratula!$D$69)))</f>
-        <v>46433</v>
+        <v>46461</v>
       </c>
       <c r="D30" s="76">
         <f>IF(OR($B31=""),"",$C30-Cáratula!$G$38)</f>
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E30" s="76">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F30" s="79">
         <f t="shared" si="2"/>
-        <v>79922.186291039689</v>
+        <v>19683.010110098123</v>
       </c>
       <c r="G30" s="79">
         <f t="shared" si="3"/>
-        <v>79061.066462247589</v>
+        <v>18673.005923096971</v>
       </c>
       <c r="H30" s="80">
         <f>IF(OR($B31=""),$B31,(Cáratula!$K$39/365*E30))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.1452190664090662E-3</v>
       </c>
       <c r="I30" s="79">
         <f t="shared" si="4"/>
-        <v>712.96646016881914</v>
+        <v>152.09572387197886</v>
       </c>
       <c r="J30" s="82">
         <f>IF(OR($B31=""),"",IF(C28="",Cáratula!$P$40*E30*G29,Cáratula!$P$40*E30*G30))</f>
-        <v>61.802793773354331</v>
+        <v>13.184267677953882</v>
       </c>
       <c r="K30" s="82">
         <f t="shared" si="5"/>
-        <v>869.55848510123315</v>
+        <v>1037.6104255606883</v>
       </c>
       <c r="L30" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M30" s="82">
         <f>IF(OR($B31=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N30" s="76"/>
       <c r="O30" s="76"/>
       <c r="P30" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="31" spans="2:23" x14ac:dyDescent="0.3">
@@ -5789,7 +5791,7 @@
       </c>
       <c r="C31" s="85">
         <f>IF(OR($B32=""),$B32,IF(DAY(EOMONTH($C30,1))&lt;Cáratula!$D$69,EOMONTH($C30,1),DATE(YEAR(EOMONTH($C30,1)),MONTH(EOMONTH($C30,1)),Cáratula!$D$69)))</f>
-        <v>46461</v>
+        <v>46492</v>
       </c>
       <c r="D31" s="84">
         <f>IF(OR($B32=""),"",$C31-Cáratula!$G$38)</f>
@@ -5797,45 +5799,45 @@
       </c>
       <c r="E31" s="84">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F31" s="86">
         <f t="shared" si="2"/>
-        <v>79061.066462247589</v>
+        <v>18673.005923096971</v>
       </c>
       <c r="G31" s="86">
         <f t="shared" si="3"/>
-        <v>78191.50797714635</v>
+        <v>17635.395497536283</v>
       </c>
       <c r="H31" s="87">
         <f>IF(OR($B32=""),$B32,(Cáratula!$K$39/365*E31))</f>
-        <v>8.1452190664090662E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I31" s="86">
         <f t="shared" si="4"/>
-        <v>636.88696160672907</v>
+        <v>159.03460532700399</v>
       </c>
       <c r="J31" s="88">
         <f>IF(OR($B32=""),"",IF(C29="",Cáratula!$P$40*E31*G30,Cáratula!$P$40*E31*G31))</f>
-        <v>55.207917544674906</v>
+        <v>13.78575776695628</v>
       </c>
       <c r="K31" s="88">
         <f t="shared" si="5"/>
-        <v>952.23285989200258</v>
+        <v>1030.0700540166606</v>
       </c>
       <c r="L31" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M31" s="88">
         <f>IF(OR($B32=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N31" s="84"/>
       <c r="O31" s="84"/>
       <c r="P31" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
@@ -5845,53 +5847,53 @@
       </c>
       <c r="C32" s="77">
         <f>IF(OR($B33=""),$B33,IF(DAY(EOMONTH($C31,1))&lt;Cáratula!$D$69,EOMONTH($C31,1),DATE(YEAR(EOMONTH($C31,1)),MONTH(EOMONTH($C31,1)),Cáratula!$D$69)))</f>
-        <v>46492</v>
+        <v>46522</v>
       </c>
       <c r="D32" s="76">
         <f>IF(OR($B33=""),"",$C32-Cáratula!$G$38)</f>
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E32" s="76">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F32" s="79">
         <f t="shared" si="2"/>
-        <v>78191.50797714635</v>
+        <v>17635.395497536283</v>
       </c>
       <c r="G32" s="79">
         <f t="shared" si="3"/>
-        <v>77239.27511725435</v>
+        <v>16605.325443519621</v>
       </c>
       <c r="H32" s="80">
         <f>IF(OR($B33=""),$B33,(Cáratula!$K$39/365*E32))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I32" s="79">
         <f t="shared" si="4"/>
-        <v>696.53768954217651</v>
+        <v>144.91501436408959</v>
       </c>
       <c r="J32" s="82">
         <f>IF(OR($B33=""),"",IF(C30="",Cáratula!$P$40*E32*G31,Cáratula!$P$40*E32*G32))</f>
-        <v>60.378682009741041</v>
+        <v>12.561814962916815</v>
       </c>
       <c r="K32" s="82">
         <f t="shared" si="5"/>
-        <v>887.41136749148905</v>
+        <v>1045.4135877836147</v>
       </c>
       <c r="L32" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M32" s="82">
         <f>IF(OR($B33=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N32" s="76"/>
       <c r="O32" s="76"/>
       <c r="P32" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
@@ -5901,7 +5903,7 @@
       </c>
       <c r="C33" s="85">
         <f>IF(OR($B34=""),$B34,IF(DAY(EOMONTH($C32,1))&lt;Cáratula!$D$69,EOMONTH($C32,1),DATE(YEAR(EOMONTH($C32,1)),MONTH(EOMONTH($C32,1)),Cáratula!$D$69)))</f>
-        <v>46522</v>
+        <v>46553</v>
       </c>
       <c r="D33" s="84">
         <f>IF(OR($B34=""),"",$C33-Cáratula!$G$38)</f>
@@ -5909,45 +5911,45 @@
       </c>
       <c r="E33" s="84">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F33" s="86">
         <f t="shared" si="2"/>
-        <v>77239.27511725435</v>
+        <v>16605.325443519621</v>
       </c>
       <c r="G33" s="86">
         <f t="shared" si="3"/>
-        <v>76351.863749762866</v>
+        <v>15559.911855736007</v>
       </c>
       <c r="H33" s="87">
         <f>IF(OR($B34=""),$B34,(Cáratula!$K$39/365*E33))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I33" s="86">
         <f t="shared" si="4"/>
-        <v>666.32427468260971</v>
+        <v>140.31805758173385</v>
       </c>
       <c r="J33" s="88">
         <f>IF(OR($B34=""),"",IF(C31="",Cáratula!$P$40*E33*G32,Cáratula!$P$40*E33*G33))</f>
-        <v>57.759661968724714</v>
+        <v>12.163332302263068</v>
       </c>
       <c r="K33" s="88">
         <f t="shared" si="5"/>
-        <v>920.24380239207221</v>
+        <v>1050.4090272266239</v>
       </c>
       <c r="L33" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M33" s="88">
         <f>IF(OR($B34=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N33" s="84"/>
       <c r="O33" s="84"/>
       <c r="P33" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.3">
@@ -5957,53 +5959,53 @@
       </c>
       <c r="C34" s="77">
         <f>IF(OR($B35=""),$B35,IF(DAY(EOMONTH($C33,1))&lt;Cáratula!$D$69,EOMONTH($C33,1),DATE(YEAR(EOMONTH($C33,1)),MONTH(EOMONTH($C33,1)),Cáratula!$D$69)))</f>
-        <v>46553</v>
+        <v>46583</v>
       </c>
       <c r="D34" s="76">
         <f>IF(OR($B35=""),"",$C34-Cáratula!$G$38)</f>
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E34" s="76">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F34" s="79">
         <f t="shared" si="2"/>
-        <v>76351.863749762866</v>
+        <v>15559.911855736007</v>
       </c>
       <c r="G34" s="79">
         <f t="shared" si="3"/>
-        <v>75431.619947370797</v>
+        <v>14509.502828509383</v>
       </c>
       <c r="H34" s="80">
         <f>IF(OR($B35=""),$B35,(Cáratula!$K$39/365*E34))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I34" s="79">
         <f t="shared" si="4"/>
-        <v>680.23639782745931</v>
+        <v>126.62472758881169</v>
       </c>
       <c r="J34" s="82">
         <f>IF(OR($B35=""),"",IF(C32="",Cáratula!$P$40*E34*G33,Cáratula!$P$40*E34*G34))</f>
-        <v>58.965620629763357</v>
+        <v>10.976339509610987</v>
       </c>
       <c r="K34" s="82">
         <f t="shared" si="5"/>
-        <v>905.12572058618389</v>
+        <v>1065.2893500121982</v>
       </c>
       <c r="L34" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M34" s="82">
         <f>IF(OR($B35=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N34" s="76"/>
       <c r="O34" s="76"/>
       <c r="P34" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
@@ -6013,7 +6015,7 @@
       </c>
       <c r="C35" s="85">
         <f>IF(OR($B36=""),$B36,IF(DAY(EOMONTH($C34,1))&lt;Cáratula!$D$69,EOMONTH($C34,1),DATE(YEAR(EOMONTH($C34,1)),MONTH(EOMONTH($C34,1)),Cáratula!$D$69)))</f>
-        <v>46583</v>
+        <v>46614</v>
       </c>
       <c r="D35" s="84">
         <f>IF(OR($B36=""),"",$C35-Cáratula!$G$38)</f>
@@ -6021,45 +6023,45 @@
       </c>
       <c r="E35" s="84">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F35" s="86">
         <f t="shared" si="2"/>
-        <v>75431.619947370797</v>
+        <v>14509.502828509383</v>
       </c>
       <c r="G35" s="86">
         <f t="shared" si="3"/>
-        <v>74526.49422678462</v>
+        <v>13444.213478497186</v>
       </c>
       <c r="H35" s="87">
         <f>IF(OR($B36=""),$B36,(Cáratula!$K$39/365*E35))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I35" s="86">
         <f t="shared" si="4"/>
-        <v>650.39423756639076</v>
+        <v>121.23885652485001</v>
       </c>
       <c r="J35" s="88">
         <f>IF(OR($B36=""),"",IF(C33="",Cáratula!$P$40*E35*G34,Cáratula!$P$40*E35*G35))</f>
-        <v>56.378782427122651</v>
+        <v>10.509470593256797</v>
       </c>
       <c r="K35" s="88">
         <f t="shared" si="5"/>
-        <v>937.55471904989315</v>
+        <v>1071.1420899925142</v>
       </c>
       <c r="L35" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M35" s="88">
         <f>IF(OR($B36=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N35" s="84"/>
       <c r="O35" s="84"/>
       <c r="P35" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
@@ -6069,7 +6071,7 @@
       </c>
       <c r="C36" s="77">
         <f>IF(OR($B37=""),$B37,IF(DAY(EOMONTH($C35,1))&lt;Cáratula!$D$69,EOMONTH($C35,1),DATE(YEAR(EOMONTH($C35,1)),MONTH(EOMONTH($C35,1)),Cáratula!$D$69)))</f>
-        <v>46614</v>
+        <v>46645</v>
       </c>
       <c r="D36" s="76">
         <f>IF(OR($B37=""),"",$C36-Cáratula!$G$38)</f>
@@ -6081,11 +6083,11 @@
       </c>
       <c r="F36" s="79">
         <f t="shared" si="2"/>
-        <v>74526.49422678462</v>
+        <v>13444.213478497186</v>
       </c>
       <c r="G36" s="79">
         <f t="shared" si="3"/>
-        <v>73588.939507734729</v>
+        <v>12373.071388504672</v>
       </c>
       <c r="H36" s="80">
         <f>IF(OR($B37=""),$B37,(Cáratula!$K$39/365*E36))</f>
@@ -6093,29 +6095,29 @@
       </c>
       <c r="I36" s="79">
         <f t="shared" si="4"/>
-        <v>663.61925099328414</v>
+        <v>111.57938166051255</v>
       </c>
       <c r="J36" s="82">
         <f>IF(OR($B37=""),"",IF(C34="",Cáratula!$P$40*E36*G35,Cáratula!$P$40*E36*G36))</f>
-        <v>57.525179660561378</v>
+        <v>9.6721485502841276</v>
       </c>
       <c r="K36" s="82">
         <f t="shared" si="5"/>
-        <v>923.18330838956103</v>
+        <v>1081.6388868998242</v>
       </c>
       <c r="L36" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M36" s="82">
         <f>IF(OR($B37=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N36" s="76"/>
       <c r="O36" s="76"/>
       <c r="P36" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
@@ -6125,53 +6127,53 @@
       </c>
       <c r="C37" s="85">
         <f>IF(OR($B38=""),$B38,IF(DAY(EOMONTH($C36,1))&lt;Cáratula!$D$69,EOMONTH($C36,1),DATE(YEAR(EOMONTH($C36,1)),MONTH(EOMONTH($C36,1)),Cáratula!$D$69)))</f>
-        <v>46645</v>
+        <v>46675</v>
       </c>
       <c r="D37" s="84">
         <f>IF(OR($B38=""),"",$C37-Cáratula!$G$38)</f>
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E37" s="84">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F37" s="86">
         <f t="shared" si="2"/>
-        <v>73588.939507734729</v>
+        <v>12373.071388504672</v>
       </c>
       <c r="G37" s="86">
         <f t="shared" si="3"/>
-        <v>72665.756199345167</v>
+        <v>11291.432501604848</v>
       </c>
       <c r="H37" s="87">
         <f>IF(OR($B38=""),$B38,(Cáratula!$K$39/365*E37))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I37" s="86">
         <f t="shared" si="4"/>
-        <v>655.29405674886118</v>
+        <v>98.540562106224471</v>
       </c>
       <c r="J37" s="88">
         <f>IF(OR($B38=""),"",IF(C35="",Cáratula!$P$40*E37*G36,Cáratula!$P$40*E37*G37))</f>
-        <v>56.803518415950577</v>
+        <v>8.5418913488852883</v>
       </c>
       <c r="K37" s="88">
         <f t="shared" si="5"/>
-        <v>932.23016387859479</v>
+        <v>1095.8079636555112</v>
       </c>
       <c r="L37" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M37" s="88">
         <f>IF(OR($B38=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N37" s="84"/>
       <c r="O37" s="84"/>
       <c r="P37" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
@@ -6181,7 +6183,7 @@
       </c>
       <c r="C38" s="77">
         <f>IF(OR($B39=""),$B39,IF(DAY(EOMONTH($C37,1))&lt;Cáratula!$D$69,EOMONTH($C37,1),DATE(YEAR(EOMONTH($C37,1)),MONTH(EOMONTH($C37,1)),Cáratula!$D$69)))</f>
-        <v>46675</v>
+        <v>46706</v>
       </c>
       <c r="D38" s="76">
         <f>IF(OR($B39=""),"",$C38-Cáratula!$G$38)</f>
@@ -6189,45 +6191,45 @@
       </c>
       <c r="E38" s="76">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F38" s="79">
         <f t="shared" si="2"/>
-        <v>72665.756199345167</v>
+        <v>11291.432501604848</v>
       </c>
       <c r="G38" s="79">
         <f t="shared" si="3"/>
-        <v>71733.526035466566</v>
+        <v>10195.624537949338</v>
       </c>
       <c r="H38" s="80">
         <f>IF(OR($B39=""),$B39,(Cáratula!$K$39/365*E38))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I38" s="79">
         <f t="shared" si="4"/>
-        <v>626.01994710517874</v>
+        <v>91.943337742644474</v>
       </c>
       <c r="J38" s="82">
         <f>IF(OR($B39=""),"",IF(C36="",Cáratula!$P$40*E38*G37,Cáratula!$P$40*E38*G38))</f>
-        <v>54.265921120309663</v>
+        <v>7.9700174675776898</v>
       </c>
       <c r="K38" s="82">
         <f t="shared" si="5"/>
-        <v>964.04187081791815</v>
+        <v>1102.9770619003989</v>
       </c>
       <c r="L38" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M38" s="82">
         <f>IF(OR($B39=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N38" s="76"/>
       <c r="O38" s="76"/>
       <c r="P38" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
@@ -6237,53 +6239,53 @@
       </c>
       <c r="C39" s="85">
         <f>IF(OR($B40=""),$B40,IF(DAY(EOMONTH($C38,1))&lt;Cáratula!$D$69,EOMONTH($C38,1),DATE(YEAR(EOMONTH($C38,1)),MONTH(EOMONTH($C38,1)),Cáratula!$D$69)))</f>
-        <v>46706</v>
+        <v>46736</v>
       </c>
       <c r="D39" s="84">
         <f>IF(OR($B40=""),"",$C39-Cáratula!$G$38)</f>
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E39" s="84">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F39" s="86">
         <f t="shared" si="2"/>
-        <v>71733.526035466566</v>
+        <v>10195.624537949338</v>
       </c>
       <c r="G39" s="86">
         <f t="shared" si="3"/>
-        <v>70769.484164648646</v>
+        <v>9092.6474760489382</v>
       </c>
       <c r="H39" s="87">
         <f>IF(OR($B40=""),$B40,(Cáratula!$K$39/365*E39))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I39" s="86">
         <f t="shared" si="4"/>
-        <v>638.19362513831254</v>
+        <v>79.351720270767956</v>
       </c>
       <c r="J39" s="88">
         <f>IF(OR($B40=""),"",IF(C37="",Cáratula!$P$40*E39*G38,Cáratula!$P$40*E39*G39))</f>
-        <v>55.321184382997835</v>
+        <v>6.8785255372236511</v>
       </c>
       <c r="K39" s="88">
         <f t="shared" si="5"/>
-        <v>950.81292952209628</v>
+        <v>1116.6601713026294</v>
       </c>
       <c r="L39" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M39" s="88">
         <f>IF(OR($B40=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N39" s="84"/>
       <c r="O39" s="84"/>
       <c r="P39" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
@@ -6293,7 +6295,7 @@
       </c>
       <c r="C40" s="77">
         <f>IF(OR($B41=""),$B41,IF(DAY(EOMONTH($C39,1))&lt;Cáratula!$D$69,EOMONTH($C39,1),DATE(YEAR(EOMONTH($C39,1)),MONTH(EOMONTH($C39,1)),Cáratula!$D$69)))</f>
-        <v>46736</v>
+        <v>46767</v>
       </c>
       <c r="D40" s="76">
         <f>IF(OR($B41=""),"",$C40-Cáratula!$G$38)</f>
@@ -6301,45 +6303,45 @@
       </c>
       <c r="E40" s="76">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F40" s="79">
         <f t="shared" si="2"/>
-        <v>70769.484164648646</v>
+        <v>9092.6474760489382</v>
       </c>
       <c r="G40" s="79">
         <f t="shared" si="3"/>
-        <v>69818.671235126545</v>
+        <v>7975.9873047463088</v>
       </c>
       <c r="H40" s="80">
         <f>IF(OR($B41=""),$B41,(Cáratula!$K$39/365*E40))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I40" s="79">
         <f t="shared" si="4"/>
-        <v>609.30897014539175</v>
+        <v>71.926824282490898</v>
       </c>
       <c r="J40" s="82">
         <f>IF(OR($B41=""),"",IF(C38="",Cáratula!$P$40*E40*G39,Cáratula!$P$40*E40*G40))</f>
-        <v>52.817346579296277</v>
+        <v>6.2349057581902345</v>
       </c>
       <c r="K40" s="82">
         <f t="shared" si="5"/>
-        <v>982.20142231871864</v>
+        <v>1124.7286870699397</v>
       </c>
       <c r="L40" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M40" s="82">
         <f>IF(OR($B41=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N40" s="76"/>
       <c r="O40" s="76"/>
       <c r="P40" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
@@ -6349,7 +6351,7 @@
       </c>
       <c r="C41" s="85">
         <f>IF(OR($B42=""),$B42,IF(DAY(EOMONTH($C40,1))&lt;Cáratula!$D$69,EOMONTH($C40,1),DATE(YEAR(EOMONTH($C40,1)),MONTH(EOMONTH($C40,1)),Cáratula!$D$69)))</f>
-        <v>46767</v>
+        <v>46798</v>
       </c>
       <c r="D41" s="84">
         <f>IF(OR($B42=""),"",$C41-Cáratula!$G$38)</f>
@@ -6361,11 +6363,11 @@
       </c>
       <c r="F41" s="86">
         <f t="shared" si="2"/>
-        <v>69818.671235126545</v>
+        <v>7975.9873047463088</v>
       </c>
       <c r="G41" s="86">
         <f t="shared" si="3"/>
-        <v>68836.469812807831</v>
+        <v>6851.2586176763689</v>
       </c>
       <c r="H41" s="87">
         <f>IF(OR($B42=""),$B42,(Cáratula!$K$39/365*E41))</f>
@@ -6373,29 +6375,29 @@
       </c>
       <c r="I41" s="86">
         <f t="shared" si="4"/>
-        <v>620.76185421038599</v>
+        <v>61.784109713196663</v>
       </c>
       <c r="J41" s="88">
         <f>IF(OR($B42=""),"",IF(C39="",Cáratula!$P$40*E41*G40,Cáratula!$P$40*E41*G41))</f>
-        <v>53.810128528409813</v>
+        <v>5.3556945584380609</v>
       </c>
       <c r="K41" s="88">
         <f t="shared" si="5"/>
-        <v>969.75575630461083</v>
+        <v>1135.7506128389864</v>
       </c>
       <c r="L41" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M41" s="88">
         <f>IF(OR($B42=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N41" s="84"/>
       <c r="O41" s="84"/>
       <c r="P41" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
@@ -6405,53 +6407,53 @@
       </c>
       <c r="C42" s="77">
         <f>IF(OR($B43=""),$B43,IF(DAY(EOMONTH($C41,1))&lt;Cáratula!$D$69,EOMONTH($C41,1),DATE(YEAR(EOMONTH($C41,1)),MONTH(EOMONTH($C41,1)),Cáratula!$D$69)))</f>
-        <v>46798</v>
+        <v>46827</v>
       </c>
       <c r="D42" s="76">
         <f>IF(OR($B43=""),"",$C42-Cáratula!$G$38)</f>
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E42" s="76">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F42" s="79">
         <f t="shared" si="2"/>
-        <v>68836.469812807831</v>
+        <v>6851.2586176763689</v>
       </c>
       <c r="G42" s="79">
         <f t="shared" si="3"/>
-        <v>67866.714056503217</v>
+        <v>5715.508004837382</v>
       </c>
       <c r="H42" s="80">
         <f>IF(OR($B43=""),$B43,(Cáratula!$K$39/365*E42))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.4361197473522467E-3</v>
       </c>
       <c r="I42" s="79">
         <f t="shared" si="4"/>
-        <v>612.01667330480097</v>
+        <v>48.216709945758481</v>
       </c>
       <c r="J42" s="82">
         <f>IF(OR($B43=""),"",IF(C40="",Cáratula!$P$40*E42*G41,Cáratula!$P$40*E42*G42))</f>
-        <v>53.05206115467869</v>
+        <v>4.1796179030662319</v>
       </c>
       <c r="K42" s="82">
         <f t="shared" si="5"/>
-        <v>979.25900458392687</v>
+        <v>1150.4940892617963</v>
       </c>
       <c r="L42" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M42" s="82">
         <f>IF(OR($B43=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N42" s="76"/>
       <c r="O42" s="76"/>
       <c r="P42" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
@@ -6461,7 +6463,7 @@
       </c>
       <c r="C43" s="85">
         <f>IF(OR($B44=""),$B44,IF(DAY(EOMONTH($C42,1))&lt;Cáratula!$D$69,EOMONTH($C42,1),DATE(YEAR(EOMONTH($C42,1)),MONTH(EOMONTH($C42,1)),Cáratula!$D$69)))</f>
-        <v>46827</v>
+        <v>46858</v>
       </c>
       <c r="D43" s="84">
         <f>IF(OR($B44=""),"",$C43-Cáratula!$G$38)</f>
@@ -6469,45 +6471,45 @@
       </c>
       <c r="E43" s="84">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F43" s="86">
         <f t="shared" si="2"/>
-        <v>67866.714056503217</v>
+        <v>5715.508004837382</v>
       </c>
       <c r="G43" s="86">
         <f t="shared" si="3"/>
-        <v>66887.455051919285</v>
+        <v>4565.013915575586</v>
       </c>
       <c r="H43" s="87">
         <f>IF(OR($B44=""),$B44,(Cáratula!$K$39/365*E43))</f>
-        <v>8.4361197473522467E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I43" s="86">
         <f t="shared" si="4"/>
-        <v>564.27058041363205</v>
+        <v>41.166935353237079</v>
       </c>
       <c r="J43" s="88">
         <f>IF(OR($B44=""),"",IF(C41="",Cáratula!$P$40*E43*G42,Cáratula!$P$40*E43*G43))</f>
-        <v>48.913238226405724</v>
+        <v>3.5685151519114751</v>
       </c>
       <c r="K43" s="88">
         <f t="shared" si="5"/>
-        <v>1031.1439204033691</v>
+        <v>1158.1549666054725</v>
       </c>
       <c r="L43" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M43" s="88">
         <f>IF(OR($B44=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N43" s="84"/>
       <c r="O43" s="84"/>
       <c r="P43" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
@@ -6517,53 +6519,53 @@
       </c>
       <c r="C44" s="77">
         <f>IF(OR($B45=""),$B45,IF(DAY(EOMONTH($C43,1))&lt;Cáratula!$D$69,EOMONTH($C43,1),DATE(YEAR(EOMONTH($C43,1)),MONTH(EOMONTH($C43,1)),Cáratula!$D$69)))</f>
-        <v>46858</v>
+        <v>46888</v>
       </c>
       <c r="D44" s="76">
         <f>IF(OR($B45=""),"",$C44-Cáratula!$G$38)</f>
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E44" s="76">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44" s="79">
         <f t="shared" si="2"/>
-        <v>66887.455051919285</v>
+        <v>4565.013915575586</v>
       </c>
       <c r="G44" s="79">
         <f t="shared" si="3"/>
-        <v>65856.311131515919</v>
+        <v>3406.8589489701135</v>
       </c>
       <c r="H44" s="80">
         <f>IF(OR($B45=""),$B45,(Cáratula!$K$39/365*E44))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I44" s="79">
         <f t="shared" si="4"/>
-        <v>593.887018329483</v>
+        <v>29.731727643983273</v>
       </c>
       <c r="J44" s="82">
         <f>IF(OR($B45=""),"",IF(C42="",Cáratula!$P$40*E44*G43,Cáratula!$P$40*E44*G44))</f>
-        <v>51.480509910379858</v>
+        <v>2.5772654602455551</v>
       </c>
       <c r="K44" s="82">
         <f t="shared" si="5"/>
-        <v>998.96021080354376</v>
+        <v>1170.5814240063921</v>
       </c>
       <c r="L44" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M44" s="82">
         <f>IF(OR($B45=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N44" s="76"/>
       <c r="O44" s="76"/>
       <c r="P44" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
@@ -6573,7 +6575,7 @@
       </c>
       <c r="C45" s="85">
         <f>IF(OR($B46=""),$B46,IF(DAY(EOMONTH($C44,1))&lt;Cáratula!$D$69,EOMONTH($C44,1),DATE(YEAR(EOMONTH($C44,1)),MONTH(EOMONTH($C44,1)),Cáratula!$D$69)))</f>
-        <v>46888</v>
+        <v>46919</v>
       </c>
       <c r="D45" s="84">
         <f>IF(OR($B46=""),"",$C45-Cáratula!$G$38)</f>
@@ -6581,45 +6583,45 @@
       </c>
       <c r="E45" s="84">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F45" s="86">
         <f t="shared" si="2"/>
-        <v>65856.311131515919</v>
+        <v>3406.8589489701135</v>
       </c>
       <c r="G45" s="86">
         <f t="shared" si="3"/>
-        <v>64857.350920712372</v>
+        <v>2236.2775249637216</v>
       </c>
       <c r="H45" s="87">
         <f>IF(OR($B46=""),$B46,(Cáratula!$K$39/365*E45))</f>
-        <v>8.7270204282954289E-3</v>
+        <v>9.0179211092386094E-3</v>
       </c>
       <c r="I45" s="86">
         <f t="shared" si="4"/>
-        <v>566.01142641018225</v>
+        <v>20.166574298486218</v>
       </c>
       <c r="J45" s="88">
         <f>IF(OR($B46=""),"",IF(C43="",Cáratula!$P$40*E45*G44,Cáratula!$P$40*E45*G45))</f>
-        <v>49.064141743087944</v>
+        <v>1.7481195850212299</v>
       </c>
       <c r="K45" s="88">
         <f t="shared" si="5"/>
-        <v>1029.2521708901363</v>
+        <v>1180.9757232271136</v>
       </c>
       <c r="L45" s="88">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M45" s="88">
         <f>IF(OR($B46=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N45" s="84"/>
       <c r="O45" s="84"/>
       <c r="P45" s="88">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.3">
@@ -6629,2747 +6631,2747 @@
       </c>
       <c r="C46" s="77">
         <f>IF(OR($B47=""),$B47,IF(DAY(EOMONTH($C45,1))&lt;Cáratula!$D$69,EOMONTH($C45,1),DATE(YEAR(EOMONTH($C45,1)),MONTH(EOMONTH($C45,1)),Cáratula!$D$69)))</f>
-        <v>46919</v>
+        <v>46949</v>
       </c>
       <c r="D46" s="76">
         <f>IF(OR($B47=""),"",$C46-Cáratula!$G$38)</f>
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E46" s="76">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46" s="79">
         <f t="shared" si="2"/>
-        <v>64857.350920712372</v>
+        <v>2236.2775249637216</v>
       </c>
       <c r="G46" s="79">
         <f t="shared" si="3"/>
-        <v>63828.098749822238</v>
+        <v>1055.301801736608</v>
       </c>
       <c r="H46" s="80">
         <f>IF(OR($B47=""),$B47,(Cáratula!$K$39/365*E46))</f>
-        <v>9.0179211092386094E-3</v>
+        <v>8.7270204282954289E-3</v>
       </c>
       <c r="I46" s="79">
         <f t="shared" si="4"/>
-        <v>575.59675907858843</v>
+        <v>9.2096403817723509</v>
       </c>
       <c r="J46" s="82">
         <f>IF(OR($B47=""),"",IF(C44="",Cáratula!$P$40*E46*G45,Cáratula!$P$40*E46*G46))</f>
-        <v>49.895036842998024</v>
+        <v>0.79832858491921144</v>
       </c>
       <c r="K46" s="82">
         <f t="shared" si="5"/>
-        <v>1018.8359431218203</v>
+        <v>1192.8824481439294</v>
       </c>
       <c r="L46" s="82">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
+        <v>1202.890417110621</v>
       </c>
       <c r="M46" s="82">
         <f>IF(OR($B47=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N46" s="76"/>
       <c r="O46" s="76"/>
       <c r="P46" s="82">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v>1212.890417110621</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="91">
         <f>IF($B46=Cáratula!$G$35,$B$21,IF(OR($B46="",$B46=$B$21),"",$B46+1))</f>
-        <v>25</v>
-      </c>
-      <c r="C47" s="85">
+        <v>0</v>
+      </c>
+      <c r="C47" s="85" t="str">
         <f>IF(OR($B48=""),$B48,IF(DAY(EOMONTH($C46,1))&lt;Cáratula!$D$69,EOMONTH($C46,1),DATE(YEAR(EOMONTH($C46,1)),MONTH(EOMONTH($C46,1)),Cáratula!$D$69)))</f>
-        <v>46949</v>
-      </c>
-      <c r="D47" s="84">
+        <v/>
+      </c>
+      <c r="D47" s="84" t="str">
         <f>IF(OR($B48=""),"",$C47-Cáratula!$G$38)</f>
-        <v>731</v>
-      </c>
-      <c r="E47" s="84">
+        <v/>
+      </c>
+      <c r="E47" s="84" t="str">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="F47" s="86">
+        <v/>
+      </c>
+      <c r="F47" s="86" t="str">
         <f t="shared" si="2"/>
-        <v>63828.098749822238</v>
-      </c>
-      <c r="G47" s="86">
+        <v/>
+      </c>
+      <c r="G47" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>62809.262806700419</v>
-      </c>
-      <c r="H47" s="87">
+        <v/>
+      </c>
+      <c r="H47" s="87" t="str">
         <f>IF(OR($B48=""),$B48,(Cáratula!$K$39/365*E47))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I47" s="86">
+        <v/>
+      </c>
+      <c r="I47" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>548.13771960025088</v>
-      </c>
-      <c r="J47" s="88">
+        <v/>
+      </c>
+      <c r="J47" s="88" t="str">
         <f>IF(OR($B48=""),"",IF(C45="",Cáratula!$P$40*E47*G46,Cáratula!$P$40*E47*G47))</f>
-        <v>47.514777112838679</v>
-      </c>
-      <c r="K47" s="88">
+        <v/>
+      </c>
+      <c r="K47" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1048.6752423303171</v>
-      </c>
-      <c r="L47" s="88">
+        <v/>
+      </c>
+      <c r="L47" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M47" s="88">
+        <v/>
+      </c>
+      <c r="M47" s="88" t="str">
         <f>IF(OR($B48=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N47" s="84"/>
       <c r="O47" s="84"/>
-      <c r="P47" s="88">
+      <c r="P47" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B48" s="92">
+      <c r="B48" s="92" t="str">
         <f>IF($B47=Cáratula!$G$35,$B$21,IF(OR($B47="",$B47=$B$21),"",$B47+1))</f>
-        <v>26</v>
-      </c>
-      <c r="C48" s="77">
+        <v/>
+      </c>
+      <c r="C48" s="77" t="str">
         <f>IF(OR($B49=""),$B49,IF(DAY(EOMONTH($C47,1))&lt;Cáratula!$D$69,EOMONTH($C47,1),DATE(YEAR(EOMONTH($C47,1)),MONTH(EOMONTH($C47,1)),Cáratula!$D$69)))</f>
-        <v>46980</v>
-      </c>
-      <c r="D48" s="76">
+        <v/>
+      </c>
+      <c r="D48" s="76" t="str">
         <f>IF(OR($B49=""),"",$C48-Cáratula!$G$38)</f>
-        <v>762</v>
-      </c>
-      <c r="E48" s="76">
+        <v/>
+      </c>
+      <c r="E48" s="76" t="str">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="F48" s="79">
+        <v/>
+      </c>
+      <c r="F48" s="79" t="str">
         <f t="shared" ref="F48:F89" si="8">IF(OR($B49=""),"",G47)</f>
-        <v>62809.262806700419</v>
-      </c>
-      <c r="G48" s="79">
+        <v/>
+      </c>
+      <c r="G48" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>61760.5875643701</v>
-      </c>
-      <c r="H48" s="80">
+        <v/>
+      </c>
+      <c r="H48" s="80" t="str">
         <f>IF(OR($B49=""),$B49,(Cáratula!$K$39/365*E48))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I48" s="79">
+        <v/>
+      </c>
+      <c r="I48" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>556.95210631571263</v>
-      </c>
-      <c r="J48" s="82">
+        <v/>
+      </c>
+      <c r="J48" s="82" t="str">
         <f>IF(OR($B49=""),"",IF(C46="",Cáratula!$P$40*E48*G47,Cáratula!$P$40*E48*G48))</f>
-        <v>48.278843523880369</v>
-      </c>
-      <c r="K48" s="82">
+        <v/>
+      </c>
+      <c r="K48" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1039.0967892038136</v>
-      </c>
-      <c r="L48" s="82">
+        <v/>
+      </c>
+      <c r="L48" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M48" s="82">
+        <v/>
+      </c>
+      <c r="M48" s="82" t="str">
         <f>IF(OR($B49=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N48" s="76"/>
       <c r="O48" s="76"/>
-      <c r="P48" s="82">
+      <c r="P48" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B49" s="91">
+      <c r="B49" s="91" t="str">
         <f>IF($B48=Cáratula!$G$35,$B$21,IF(OR($B48="",$B48=$B$21),"",$B48+1))</f>
-        <v>27</v>
-      </c>
-      <c r="C49" s="85">
+        <v/>
+      </c>
+      <c r="C49" s="85" t="str">
         <f>IF(OR($B50=""),$B50,IF(DAY(EOMONTH($C48,1))&lt;Cáratula!$D$69,EOMONTH($C48,1),DATE(YEAR(EOMONTH($C48,1)),MONTH(EOMONTH($C48,1)),Cáratula!$D$69)))</f>
-        <v>47011</v>
-      </c>
-      <c r="D49" s="84">
+        <v/>
+      </c>
+      <c r="D49" s="84" t="str">
         <f>IF(OR($B50=""),"",$C49-Cáratula!$G$38)</f>
-        <v>793</v>
-      </c>
-      <c r="E49" s="84">
+        <v/>
+      </c>
+      <c r="E49" s="84" t="str">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="F49" s="86">
+        <v/>
+      </c>
+      <c r="F49" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>61760.5875643701</v>
-      </c>
-      <c r="G49" s="86">
+        <v/>
+      </c>
+      <c r="G49" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>60721.490775166283</v>
-      </c>
-      <c r="H49" s="87">
+        <v/>
+      </c>
+      <c r="H49" s="87" t="str">
         <f>IF(OR($B50=""),$B50,(Cáratula!$K$39/365*E49))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I49" s="86">
+        <v/>
+      </c>
+      <c r="I49" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>547.58161344580947</v>
-      </c>
-      <c r="J49" s="88">
+        <v/>
+      </c>
+      <c r="J49" s="88" t="str">
         <f>IF(OR($B50=""),"",IF(C47="",Cáratula!$P$40*E49*G48,Cáratula!$P$40*E49*G49))</f>
-        <v>47.466571599817925</v>
-      </c>
-      <c r="K49" s="88">
+        <v/>
+      </c>
+      <c r="K49" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1049.2795539977794</v>
-      </c>
-      <c r="L49" s="88">
+        <v/>
+      </c>
+      <c r="L49" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M49" s="88">
+        <v/>
+      </c>
+      <c r="M49" s="88" t="str">
         <f>IF(OR($B50=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N49" s="84"/>
       <c r="O49" s="84"/>
-      <c r="P49" s="88">
+      <c r="P49" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B50" s="92">
+      <c r="B50" s="92" t="str">
         <f>IF($B49=Cáratula!$G$35,$B$21,IF(OR($B49="",$B49=$B$21),"",$B49+1))</f>
-        <v>28</v>
-      </c>
-      <c r="C50" s="77">
+        <v/>
+      </c>
+      <c r="C50" s="77" t="str">
         <f>IF(OR($B51=""),$B51,IF(DAY(EOMONTH($C49,1))&lt;Cáratula!$D$69,EOMONTH($C49,1),DATE(YEAR(EOMONTH($C49,1)),MONTH(EOMONTH($C49,1)),Cáratula!$D$69)))</f>
-        <v>47041</v>
-      </c>
-      <c r="D50" s="76">
+        <v/>
+      </c>
+      <c r="D50" s="76" t="str">
         <f>IF(OR($B51=""),"",$C50-Cáratula!$G$38)</f>
-        <v>823</v>
-      </c>
-      <c r="E50" s="76">
+        <v/>
+      </c>
+      <c r="E50" s="76" t="str">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="F50" s="79">
+        <v/>
+      </c>
+      <c r="F50" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>60721.490775166283</v>
-      </c>
-      <c r="G50" s="79">
+        <v/>
+      </c>
+      <c r="G50" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>59672.211221168502</v>
-      </c>
-      <c r="H50" s="80">
+        <v/>
+      </c>
+      <c r="H50" s="80" t="str">
         <f>IF(OR($B51=""),$B51,(Cáratula!$K$39/365*E50))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I50" s="79">
+        <v/>
+      </c>
+      <c r="I50" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>520.76060632869724</v>
-      </c>
-      <c r="J50" s="82">
+        <v/>
+      </c>
+      <c r="J50" s="82" t="str">
         <f>IF(OR($B51=""),"",IF(C48="",Cáratula!$P$40*E50*G49,Cáratula!$P$40*E50*G50))</f>
-        <v>45.141619075038477</v>
-      </c>
-      <c r="K50" s="82">
+        <v/>
+      </c>
+      <c r="K50" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1078.4255136396707</v>
-      </c>
-      <c r="L50" s="82">
+        <v/>
+      </c>
+      <c r="L50" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M50" s="82">
+        <v/>
+      </c>
+      <c r="M50" s="82" t="str">
         <f>IF(OR($B51=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N50" s="76"/>
       <c r="O50" s="76"/>
-      <c r="P50" s="82">
+      <c r="P50" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B51" s="91">
+      <c r="B51" s="91" t="str">
         <f>IF($B50=Cáratula!$G$35,$B$21,IF(OR($B50="",$B50=$B$21),"",$B50+1))</f>
-        <v>29</v>
-      </c>
-      <c r="C51" s="85">
+        <v/>
+      </c>
+      <c r="C51" s="85" t="str">
         <f>IF(OR($B52=""),$B52,IF(DAY(EOMONTH($C50,1))&lt;Cáratula!$D$69,EOMONTH($C50,1),DATE(YEAR(EOMONTH($C50,1)),MONTH(EOMONTH($C50,1)),Cáratula!$D$69)))</f>
-        <v>47072</v>
-      </c>
-      <c r="D51" s="84">
+        <v/>
+      </c>
+      <c r="D51" s="84" t="str">
         <f>IF(OR($B52=""),"",$C51-Cáratula!$G$38)</f>
-        <v>854</v>
-      </c>
-      <c r="E51" s="84">
+        <v/>
+      </c>
+      <c r="E51" s="84" t="str">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="F51" s="86">
+        <v/>
+      </c>
+      <c r="F51" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>59672.211221168502</v>
-      </c>
-      <c r="G51" s="86">
+        <v/>
+      </c>
+      <c r="G51" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>58593.785707528834</v>
-      </c>
-      <c r="H51" s="87">
+        <v/>
+      </c>
+      <c r="H51" s="87" t="str">
         <f>IF(OR($B52=""),$B52,(Cáratula!$K$39/365*E51))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I51" s="86">
+        <v/>
+      </c>
+      <c r="I51" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>528.39413700212776</v>
-      </c>
-      <c r="J51" s="88">
+        <v/>
+      </c>
+      <c r="J51" s="88" t="str">
         <f>IF(OR($B52=""),"",IF(C49="",Cáratula!$P$40*E51*G50,Cáratula!$P$40*E51*G51))</f>
-        <v>45.803324145794399</v>
-      </c>
-      <c r="K51" s="88">
+        <v/>
+      </c>
+      <c r="K51" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1070.1302778954844</v>
-      </c>
-      <c r="L51" s="88">
+        <v/>
+      </c>
+      <c r="L51" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M51" s="88">
+        <v/>
+      </c>
+      <c r="M51" s="88" t="str">
         <f>IF(OR($B52=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N51" s="84"/>
       <c r="O51" s="84"/>
-      <c r="P51" s="88">
+      <c r="P51" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B52" s="92">
+      <c r="B52" s="92" t="str">
         <f>IF($B51=Cáratula!$G$35,$B$21,IF(OR($B51="",$B51=$B$21),"",$B51+1))</f>
-        <v>30</v>
-      </c>
-      <c r="C52" s="77">
+        <v/>
+      </c>
+      <c r="C52" s="77" t="str">
         <f>IF(OR($B53=""),$B53,IF(DAY(EOMONTH($C51,1))&lt;Cáratula!$D$69,EOMONTH($C51,1),DATE(YEAR(EOMONTH($C51,1)),MONTH(EOMONTH($C51,1)),Cáratula!$D$69)))</f>
-        <v>47102</v>
-      </c>
-      <c r="D52" s="76">
+        <v/>
+      </c>
+      <c r="D52" s="76" t="str">
         <f>IF(OR($B53=""),"",$C52-Cáratula!$G$38)</f>
-        <v>884</v>
-      </c>
-      <c r="E52" s="76">
+        <v/>
+      </c>
+      <c r="E52" s="76" t="str">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="F52" s="79">
+        <v/>
+      </c>
+      <c r="F52" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>58593.785707528834</v>
-      </c>
-      <c r="G52" s="79">
+        <v/>
+      </c>
+      <c r="G52" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>57523.655429633349</v>
-      </c>
-      <c r="H52" s="80">
+        <v/>
+      </c>
+      <c r="H52" s="80" t="str">
         <f>IF(OR($B53=""),$B53,(Cáratula!$K$39/365*E52))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I52" s="79">
+        <v/>
+      </c>
+      <c r="I52" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>502.01011604463753</v>
-      </c>
-      <c r="J52" s="82">
+        <v/>
+      </c>
+      <c r="J52" s="82" t="str">
         <f>IF(OR($B53=""),"",IF(C50="",Cáratula!$P$40*E52*G51,Cáratula!$P$40*E52*G52))</f>
-        <v>43.516251334877694</v>
-      </c>
-      <c r="K52" s="82">
+        <v/>
+      </c>
+      <c r="K52" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1098.8013716638914</v>
-      </c>
-      <c r="L52" s="82">
+        <v/>
+      </c>
+      <c r="L52" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M52" s="82">
+        <v/>
+      </c>
+      <c r="M52" s="82" t="str">
         <f>IF(OR($B53=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N52" s="76"/>
       <c r="O52" s="76"/>
-      <c r="P52" s="82">
+      <c r="P52" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B53" s="91">
+      <c r="B53" s="91" t="str">
         <f>IF($B52=Cáratula!$G$35,$B$21,IF(OR($B52="",$B52=$B$21),"",$B52+1))</f>
-        <v>31</v>
-      </c>
-      <c r="C53" s="85">
+        <v/>
+      </c>
+      <c r="C53" s="85" t="str">
         <f>IF(OR($B54=""),$B54,IF(DAY(EOMONTH($C52,1))&lt;Cáratula!$D$69,EOMONTH($C52,1),DATE(YEAR(EOMONTH($C52,1)),MONTH(EOMONTH($C52,1)),Cáratula!$D$69)))</f>
-        <v>47133</v>
-      </c>
-      <c r="D53" s="84">
+        <v/>
+      </c>
+      <c r="D53" s="84" t="str">
         <f>IF(OR($B54=""),"",$C53-Cáratula!$G$38)</f>
-        <v>915</v>
-      </c>
-      <c r="E53" s="84">
+        <v/>
+      </c>
+      <c r="E53" s="84" t="str">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="F53" s="86">
+        <v/>
+      </c>
+      <c r="F53" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>57523.655429633349</v>
-      </c>
-      <c r="G53" s="86">
+        <v/>
+      </c>
+      <c r="G53" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>56424.85405796946</v>
-      </c>
-      <c r="H53" s="87">
+        <v/>
+      </c>
+      <c r="H53" s="87" t="str">
         <f>IF(OR($B54=""),$B54,(Cáratula!$K$39/365*E53))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I53" s="86">
+        <v/>
+      </c>
+      <c r="I53" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>508.83488249507059</v>
-      </c>
-      <c r="J53" s="88">
+        <v/>
+      </c>
+      <c r="J53" s="88" t="str">
         <f>IF(OR($B54=""),"",IF(C51="",Cáratula!$P$40*E53*G52,Cáratula!$P$40*E53*G53))</f>
-        <v>44.107849477359117</v>
-      </c>
-      <c r="K53" s="88">
+        <v/>
+      </c>
+      <c r="K53" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1091.3850070709768</v>
-      </c>
-      <c r="L53" s="88">
+        <v/>
+      </c>
+      <c r="L53" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M53" s="88">
+        <v/>
+      </c>
+      <c r="M53" s="88" t="str">
         <f>IF(OR($B54=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N53" s="84"/>
       <c r="O53" s="84"/>
-      <c r="P53" s="88">
+      <c r="P53" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B54" s="92">
+      <c r="B54" s="92" t="str">
         <f>IF($B53=Cáratula!$G$35,$B$21,IF(OR($B53="",$B53=$B$21),"",$B53+1))</f>
-        <v>32</v>
-      </c>
-      <c r="C54" s="77">
+        <v/>
+      </c>
+      <c r="C54" s="77" t="str">
         <f>IF(OR($B55=""),$B55,IF(DAY(EOMONTH($C53,1))&lt;Cáratula!$D$69,EOMONTH($C53,1),DATE(YEAR(EOMONTH($C53,1)),MONTH(EOMONTH($C53,1)),Cáratula!$D$69)))</f>
-        <v>47164</v>
-      </c>
-      <c r="D54" s="76">
+        <v/>
+      </c>
+      <c r="D54" s="76" t="str">
         <f>IF(OR($B55=""),"",$C54-Cáratula!$G$38)</f>
-        <v>946</v>
-      </c>
-      <c r="E54" s="76">
+        <v/>
+      </c>
+      <c r="E54" s="76" t="str">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="F54" s="79">
+        <v/>
+      </c>
+      <c r="F54" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>56424.85405796946</v>
-      </c>
-      <c r="G54" s="79">
+        <v/>
+      </c>
+      <c r="G54" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>55333.469050898486</v>
-      </c>
-      <c r="H54" s="80">
+        <v/>
+      </c>
+      <c r="H54" s="80" t="str">
         <f>IF(OR($B55=""),$B55,(Cáratula!$K$39/365*E54))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I54" s="79">
+        <v/>
+      </c>
+      <c r="I54" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>498.99285860149871</v>
-      </c>
-      <c r="J54" s="82">
+        <v/>
+      </c>
+      <c r="J54" s="82" t="str">
         <f>IF(OR($B55=""),"",IF(C52="",Cáratula!$P$40*E54*G53,Cáratula!$P$40*E54*G54))</f>
-        <v>43.254703351996049</v>
-      </c>
-      <c r="K54" s="82">
+        <v/>
+      </c>
+      <c r="K54" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1102.0801770899118</v>
-      </c>
-      <c r="L54" s="82">
+        <v/>
+      </c>
+      <c r="L54" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M54" s="82">
+        <v/>
+      </c>
+      <c r="M54" s="82" t="str">
         <f>IF(OR($B55=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N54" s="76"/>
       <c r="O54" s="76"/>
-      <c r="P54" s="82">
+      <c r="P54" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B55" s="91">
+      <c r="B55" s="91" t="str">
         <f>IF($B54=Cáratula!$G$35,$B$21,IF(OR($B54="",$B54=$B$21),"",$B54+1))</f>
-        <v>33</v>
-      </c>
-      <c r="C55" s="85">
+        <v/>
+      </c>
+      <c r="C55" s="85" t="str">
         <f>IF(OR($B56=""),$B56,IF(DAY(EOMONTH($C54,1))&lt;Cáratula!$D$69,EOMONTH($C54,1),DATE(YEAR(EOMONTH($C54,1)),MONTH(EOMONTH($C54,1)),Cáratula!$D$69)))</f>
-        <v>47192</v>
-      </c>
-      <c r="D55" s="84">
+        <v/>
+      </c>
+      <c r="D55" s="84" t="str">
         <f>IF(OR($B56=""),"",$C55-Cáratula!$G$38)</f>
-        <v>974</v>
-      </c>
-      <c r="E55" s="84">
+        <v/>
+      </c>
+      <c r="E55" s="84" t="str">
         <f t="shared" ref="E55:E88" si="9">IF(OR($B56=""),"",C55-C54)</f>
-        <v>28</v>
-      </c>
-      <c r="F55" s="86">
+        <v/>
+      </c>
+      <c r="F55" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>55333.469050898486</v>
-      </c>
-      <c r="G55" s="86">
+        <v/>
+      </c>
+      <c r="G55" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>54231.388873808573</v>
-      </c>
-      <c r="H55" s="87">
+        <v/>
+      </c>
+      <c r="H55" s="87" t="str">
         <f>IF(OR($B56=""),$B56,(Cáratula!$K$39/365*E55))</f>
-        <v>8.1452190664090662E-3</v>
-      </c>
-      <c r="I55" s="86">
+        <v/>
+      </c>
+      <c r="I55" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>441.7265426527901</v>
-      </c>
-      <c r="J55" s="88">
+        <v/>
+      </c>
+      <c r="J55" s="88" t="str">
         <f>IF(OR($B56=""),"",IF(C53="",Cáratula!$P$40*E55*G54,Cáratula!$P$40*E55*G55))</f>
-        <v>38.29062928615604</v>
-      </c>
-      <c r="K55" s="88">
+        <v/>
+      </c>
+      <c r="K55" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1164.3105671044605</v>
-      </c>
-      <c r="L55" s="88">
+        <v/>
+      </c>
+      <c r="L55" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M55" s="88">
+        <v/>
+      </c>
+      <c r="M55" s="88" t="str">
         <f>IF(OR($B56=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N55" s="84"/>
       <c r="O55" s="84"/>
-      <c r="P55" s="88">
+      <c r="P55" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B56" s="92">
+      <c r="B56" s="92" t="str">
         <f>IF($B55=Cáratula!$G$35,$B$21,IF(OR($B55="",$B55=$B$21),"",$B55+1))</f>
-        <v>34</v>
-      </c>
-      <c r="C56" s="77">
+        <v/>
+      </c>
+      <c r="C56" s="77" t="str">
         <f>IF(OR($B57=""),$B57,IF(DAY(EOMONTH($C55,1))&lt;Cáratula!$D$69,EOMONTH($C55,1),DATE(YEAR(EOMONTH($C55,1)),MONTH(EOMONTH($C55,1)),Cáratula!$D$69)))</f>
-        <v>47223</v>
-      </c>
-      <c r="D56" s="76">
+        <v/>
+      </c>
+      <c r="D56" s="76" t="str">
         <f>IF(OR($B57=""),"",$C56-Cáratula!$G$38)</f>
-        <v>1005</v>
-      </c>
-      <c r="E56" s="76">
+        <v/>
+      </c>
+      <c r="E56" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F56" s="79">
+        <v/>
+      </c>
+      <c r="F56" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>54231.388873808573</v>
-      </c>
-      <c r="G56" s="79">
+        <v/>
+      </c>
+      <c r="G56" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>53067.078306704112</v>
-      </c>
-      <c r="H56" s="80">
+        <v/>
+      </c>
+      <c r="H56" s="80" t="str">
         <f>IF(OR($B57=""),$B57,(Cáratula!$K$39/365*E56))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I56" s="79">
+        <v/>
+      </c>
+      <c r="I56" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>478.5547256676453</v>
-      </c>
-      <c r="J56" s="82">
+        <v/>
+      </c>
+      <c r="J56" s="82" t="str">
         <f>IF(OR($B57=""),"",IF(C54="",Cáratula!$P$40*E56*G55,Cáratula!$P$40*E56*G56))</f>
-        <v>41.483043974745321</v>
-      </c>
-      <c r="K56" s="82">
+        <v/>
+      </c>
+      <c r="K56" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1124.2899694010162</v>
-      </c>
-      <c r="L56" s="82">
+        <v/>
+      </c>
+      <c r="L56" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M56" s="82">
+        <v/>
+      </c>
+      <c r="M56" s="82" t="str">
         <f>IF(OR($B57=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N56" s="76"/>
       <c r="O56" s="76"/>
-      <c r="P56" s="82">
+      <c r="P56" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B57" s="91">
+      <c r="B57" s="91" t="str">
         <f>IF($B56=Cáratula!$G$35,$B$21,IF(OR($B56="",$B56=$B$21),"",$B56+1))</f>
-        <v>35</v>
-      </c>
-      <c r="C57" s="85">
+        <v/>
+      </c>
+      <c r="C57" s="85" t="str">
         <f>IF(OR($B58=""),$B58,IF(DAY(EOMONTH($C56,1))&lt;Cáratula!$D$69,EOMONTH($C56,1),DATE(YEAR(EOMONTH($C56,1)),MONTH(EOMONTH($C56,1)),Cáratula!$D$69)))</f>
-        <v>47253</v>
-      </c>
-      <c r="D57" s="84">
+        <v/>
+      </c>
+      <c r="D57" s="84" t="str">
         <f>IF(OR($B58=""),"",$C57-Cáratula!$G$38)</f>
-        <v>1035</v>
-      </c>
-      <c r="E57" s="84">
+        <v/>
+      </c>
+      <c r="E57" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F57" s="86">
+        <v/>
+      </c>
+      <c r="F57" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>53067.078306704112</v>
-      </c>
-      <c r="G57" s="86">
+        <v/>
+      </c>
+      <c r="G57" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>51942.788337303093</v>
-      </c>
-      <c r="H57" s="87">
+        <v/>
+      </c>
+      <c r="H57" s="87" t="str">
         <f>IF(OR($B58=""),$B58,(Cáratula!$K$39/365*E57))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I57" s="86">
+        <v/>
+      </c>
+      <c r="I57" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>453.30577492226962</v>
-      </c>
-      <c r="J57" s="88">
+        <v/>
+      </c>
+      <c r="J57" s="88" t="str">
         <f>IF(OR($B58=""),"",IF(C55="",Cáratula!$P$40*E57*G56,Cáratula!$P$40*E57*G57))</f>
-        <v>39.294363604646925</v>
-      </c>
-      <c r="K57" s="88">
+        <v/>
+      </c>
+      <c r="K57" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1151.7276005164902</v>
-      </c>
-      <c r="L57" s="88">
+        <v/>
+      </c>
+      <c r="L57" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M57" s="88">
+        <v/>
+      </c>
+      <c r="M57" s="88" t="str">
         <f>IF(OR($B58=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N57" s="84"/>
       <c r="O57" s="84"/>
-      <c r="P57" s="88">
+      <c r="P57" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B58" s="92">
+      <c r="B58" s="92" t="str">
         <f>IF($B57=Cáratula!$G$35,$B$21,IF(OR($B57="",$B57=$B$21),"",$B57+1))</f>
-        <v>36</v>
-      </c>
-      <c r="C58" s="77">
+        <v/>
+      </c>
+      <c r="C58" s="77" t="str">
         <f>IF(OR($B59=""),$B59,IF(DAY(EOMONTH($C57,1))&lt;Cáratula!$D$69,EOMONTH($C57,1),DATE(YEAR(EOMONTH($C57,1)),MONTH(EOMONTH($C57,1)),Cáratula!$D$69)))</f>
-        <v>47284</v>
-      </c>
-      <c r="D58" s="76">
+        <v/>
+      </c>
+      <c r="D58" s="76" t="str">
         <f>IF(OR($B59=""),"",$C58-Cáratula!$G$38)</f>
-        <v>1066</v>
-      </c>
-      <c r="E58" s="76">
+        <v/>
+      </c>
+      <c r="E58" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F58" s="79">
+        <v/>
+      </c>
+      <c r="F58" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>51942.788337303093</v>
-      </c>
-      <c r="G58" s="79">
+        <v/>
+      </c>
+      <c r="G58" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>50791.060736786603</v>
-      </c>
-      <c r="H58" s="80">
+        <v/>
+      </c>
+      <c r="H58" s="80" t="str">
         <f>IF(OR($B59=""),$B59,(Cáratula!$K$39/365*E58))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I58" s="79">
+        <v/>
+      </c>
+      <c r="I58" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>458.02977877888821</v>
-      </c>
-      <c r="J58" s="82">
+        <v/>
+      </c>
+      <c r="J58" s="82" t="str">
         <f>IF(OR($B59=""),"",IF(C56="",Cáratula!$P$40*E58*G57,Cáratula!$P$40*E58*G58))</f>
-        <v>39.703859215514797</v>
-      </c>
-      <c r="K58" s="82">
+        <v/>
+      </c>
+      <c r="K58" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1146.5941010490037</v>
-      </c>
-      <c r="L58" s="82">
+        <v/>
+      </c>
+      <c r="L58" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M58" s="82">
+        <v/>
+      </c>
+      <c r="M58" s="82" t="str">
         <f>IF(OR($B59=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N58" s="76"/>
       <c r="O58" s="76"/>
-      <c r="P58" s="82">
+      <c r="P58" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B59" s="91">
+      <c r="B59" s="91" t="str">
         <f>IF($B58=Cáratula!$G$35,$B$21,IF(OR($B58="",$B58=$B$21),"",$B58+1))</f>
-        <v>37</v>
-      </c>
-      <c r="C59" s="85">
+        <v/>
+      </c>
+      <c r="C59" s="85" t="str">
         <f>IF(OR($B60=""),$B60,IF(DAY(EOMONTH($C58,1))&lt;Cáratula!$D$69,EOMONTH($C58,1),DATE(YEAR(EOMONTH($C58,1)),MONTH(EOMONTH($C58,1)),Cáratula!$D$69)))</f>
-        <v>47314</v>
-      </c>
-      <c r="D59" s="84">
+        <v/>
+      </c>
+      <c r="D59" s="84" t="str">
         <f>IF(OR($B60=""),"",$C59-Cáratula!$G$38)</f>
-        <v>1096</v>
-      </c>
-      <c r="E59" s="84">
+        <v/>
+      </c>
+      <c r="E59" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F59" s="86">
+        <v/>
+      </c>
+      <c r="F59" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>50791.060736786603</v>
-      </c>
-      <c r="G59" s="86">
+        <v/>
+      </c>
+      <c r="G59" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>49644.466635737597</v>
-      </c>
-      <c r="H59" s="87">
+        <v/>
+      </c>
+      <c r="H59" s="87" t="str">
         <f>IF(OR($B60=""),$B60,(Cáratula!$K$39/365*E59))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I59" s="86">
+        <v/>
+      </c>
+      <c r="I59" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>433.24827448191286</v>
-      </c>
-      <c r="J59" s="88">
+        <v/>
+      </c>
+      <c r="J59" s="88" t="str">
         <f>IF(OR($B60=""),"",IF(C57="",Cáratula!$P$40*E59*G58,Cáratula!$P$40*E59*G59))</f>
-        <v>37.555698979342097</v>
-      </c>
-      <c r="K59" s="88">
+        <v/>
+      </c>
+      <c r="K59" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1173.5237655821516</v>
-      </c>
-      <c r="L59" s="88">
+        <v/>
+      </c>
+      <c r="L59" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M59" s="88">
+        <v/>
+      </c>
+      <c r="M59" s="88" t="str">
         <f>IF(OR($B60=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N59" s="84"/>
       <c r="O59" s="84"/>
-      <c r="P59" s="88">
+      <c r="P59" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B60" s="92">
+      <c r="B60" s="92" t="str">
         <f>IF($B59=Cáratula!$G$35,$B$21,IF(OR($B59="",$B59=$B$21),"",$B59+1))</f>
-        <v>38</v>
-      </c>
-      <c r="C60" s="77">
+        <v/>
+      </c>
+      <c r="C60" s="77" t="str">
         <f>IF(OR($B61=""),$B61,IF(DAY(EOMONTH($C59,1))&lt;Cáratula!$D$69,EOMONTH($C59,1),DATE(YEAR(EOMONTH($C59,1)),MONTH(EOMONTH($C59,1)),Cáratula!$D$69)))</f>
-        <v>47345</v>
-      </c>
-      <c r="D60" s="76">
+        <v/>
+      </c>
+      <c r="D60" s="76" t="str">
         <f>IF(OR($B61=""),"",$C60-Cáratula!$G$38)</f>
-        <v>1127</v>
-      </c>
-      <c r="E60" s="76">
+        <v/>
+      </c>
+      <c r="E60" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F60" s="79">
+        <v/>
+      </c>
+      <c r="F60" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>49644.466635737597</v>
-      </c>
-      <c r="G60" s="79">
+        <v/>
+      </c>
+      <c r="G60" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>48470.942870155443</v>
-      </c>
-      <c r="H60" s="80">
+        <v/>
+      </c>
+      <c r="H60" s="80" t="str">
         <f>IF(OR($B61=""),$B61,(Cáratula!$K$39/365*E60))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I60" s="79">
+        <v/>
+      </c>
+      <c r="I60" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>437.10713889347346</v>
-      </c>
-      <c r="J60" s="82">
+        <v/>
+      </c>
+      <c r="J60" s="82" t="str">
         <f>IF(OR($B61=""),"",IF(C58="",Cáratula!$P$40*E60*G59,Cáratula!$P$40*E60*G60))</f>
-        <v>37.890200831463645</v>
-      </c>
-      <c r="K60" s="82">
+        <v/>
+      </c>
+      <c r="K60" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1169.3303993184693</v>
-      </c>
-      <c r="L60" s="82">
+        <v/>
+      </c>
+      <c r="L60" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M60" s="82">
+        <v/>
+      </c>
+      <c r="M60" s="82" t="str">
         <f>IF(OR($B61=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N60" s="76"/>
       <c r="O60" s="76"/>
-      <c r="P60" s="82">
+      <c r="P60" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B61" s="91">
+      <c r="B61" s="91" t="str">
         <f>IF($B60=Cáratula!$G$35,$B$21,IF(OR($B60="",$B60=$B$21),"",$B60+1))</f>
-        <v>39</v>
-      </c>
-      <c r="C61" s="85">
+        <v/>
+      </c>
+      <c r="C61" s="85" t="str">
         <f>IF(OR($B62=""),$B62,IF(DAY(EOMONTH($C60,1))&lt;Cáratula!$D$69,EOMONTH($C60,1),DATE(YEAR(EOMONTH($C60,1)),MONTH(EOMONTH($C60,1)),Cáratula!$D$69)))</f>
-        <v>47376</v>
-      </c>
-      <c r="D61" s="84">
+        <v/>
+      </c>
+      <c r="D61" s="84" t="str">
         <f>IF(OR($B62=""),"",$C61-Cáratula!$G$38)</f>
-        <v>1158</v>
-      </c>
-      <c r="E61" s="84">
+        <v/>
+      </c>
+      <c r="E61" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F61" s="86">
+        <v/>
+      </c>
+      <c r="F61" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>48470.942870155443</v>
-      </c>
-      <c r="G61" s="86">
+        <v/>
+      </c>
+      <c r="G61" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>47301.612470836975</v>
-      </c>
-      <c r="H61" s="87">
+        <v/>
+      </c>
+      <c r="H61" s="87" t="str">
         <f>IF(OR($B62=""),$B62,(Cáratula!$K$39/365*E61))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I61" s="86">
+        <v/>
+      </c>
+      <c r="I61" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>426.56220960178501</v>
-      </c>
-      <c r="J61" s="88">
+        <v/>
+      </c>
+      <c r="J61" s="88" t="str">
         <f>IF(OR($B62=""),"",IF(C59="",Cáratula!$P$40*E61*G60,Cáratula!$P$40*E61*G61))</f>
-        <v>36.976124045559146</v>
-      </c>
-      <c r="K61" s="88">
+        <v/>
+      </c>
+      <c r="K61" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1180.7894053960624</v>
-      </c>
-      <c r="L61" s="88">
+        <v/>
+      </c>
+      <c r="L61" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M61" s="88">
+        <v/>
+      </c>
+      <c r="M61" s="88" t="str">
         <f>IF(OR($B62=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N61" s="84"/>
       <c r="O61" s="84"/>
-      <c r="P61" s="88">
+      <c r="P61" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B62" s="92">
+      <c r="B62" s="92" t="str">
         <f>IF($B61=Cáratula!$G$35,$B$21,IF(OR($B61="",$B61=$B$21),"",$B61+1))</f>
-        <v>40</v>
-      </c>
-      <c r="C62" s="77">
+        <v/>
+      </c>
+      <c r="C62" s="77" t="str">
         <f>IF(OR($B63=""),$B63,IF(DAY(EOMONTH($C61,1))&lt;Cáratula!$D$69,EOMONTH($C61,1),DATE(YEAR(EOMONTH($C61,1)),MONTH(EOMONTH($C61,1)),Cáratula!$D$69)))</f>
-        <v>47406</v>
-      </c>
-      <c r="D62" s="76">
+        <v/>
+      </c>
+      <c r="D62" s="76" t="str">
         <f>IF(OR($B63=""),"",$C62-Cáratula!$G$38)</f>
-        <v>1188</v>
-      </c>
-      <c r="E62" s="76">
+        <v/>
+      </c>
+      <c r="E62" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F62" s="79">
+        <v/>
+      </c>
+      <c r="F62" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>47301.612470836975</v>
-      </c>
-      <c r="G62" s="79">
+        <v/>
+      </c>
+      <c r="G62" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>46120.823065440913</v>
-      </c>
-      <c r="H62" s="80">
+        <v/>
+      </c>
+      <c r="H62" s="80" t="str">
         <f>IF(OR($B63=""),$B63,(Cáratula!$K$39/365*E62))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I62" s="79">
+        <v/>
+      </c>
+      <c r="I62" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>402.49736506190186</v>
-      </c>
-      <c r="J62" s="82">
+        <v/>
+      </c>
+      <c r="J62" s="82" t="str">
         <f>IF(OR($B63=""),"",IF(C60="",Cáratula!$P$40*E62*G61,Cáratula!$P$40*E62*G62))</f>
-        <v>34.890086752957657</v>
-      </c>
-      <c r="K62" s="82">
+        <v/>
+      </c>
+      <c r="K62" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1206.940287228547</v>
-      </c>
-      <c r="L62" s="82">
+        <v/>
+      </c>
+      <c r="L62" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M62" s="82">
+        <v/>
+      </c>
+      <c r="M62" s="82" t="str">
         <f>IF(OR($B63=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N62" s="76"/>
       <c r="O62" s="76"/>
-      <c r="P62" s="82">
+      <c r="P62" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B63" s="91">
+      <c r="B63" s="91" t="str">
         <f>IF($B62=Cáratula!$G$35,$B$21,IF(OR($B62="",$B62=$B$21),"",$B62+1))</f>
-        <v>41</v>
-      </c>
-      <c r="C63" s="85">
+        <v/>
+      </c>
+      <c r="C63" s="85" t="str">
         <f>IF(OR($B64=""),$B64,IF(DAY(EOMONTH($C62,1))&lt;Cáratula!$D$69,EOMONTH($C62,1),DATE(YEAR(EOMONTH($C62,1)),MONTH(EOMONTH($C62,1)),Cáratula!$D$69)))</f>
-        <v>47437</v>
-      </c>
-      <c r="D63" s="84">
+        <v/>
+      </c>
+      <c r="D63" s="84" t="str">
         <f>IF(OR($B64=""),"",$C63-Cáratula!$G$38)</f>
-        <v>1219</v>
-      </c>
-      <c r="E63" s="84">
+        <v/>
+      </c>
+      <c r="E63" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F63" s="86">
+        <v/>
+      </c>
+      <c r="F63" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>46120.823065440913</v>
-      </c>
-      <c r="G63" s="86">
+        <v/>
+      </c>
+      <c r="G63" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>44913.882778212363</v>
-      </c>
-      <c r="H63" s="87">
+        <v/>
+      </c>
+      <c r="H63" s="87" t="str">
         <f>IF(OR($B64=""),$B64,(Cáratula!$K$39/365*E63))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I63" s="86">
+        <v/>
+      </c>
+      <c r="I63" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>405.02985160350971</v>
-      </c>
-      <c r="J63" s="88">
+        <v/>
+      </c>
+      <c r="J63" s="88" t="str">
         <f>IF(OR($B64=""),"",IF(C61="",Cáratula!$P$40*E63*G62,Cáratula!$P$40*E63*G63))</f>
-        <v>35.109612848796338</v>
-      </c>
-      <c r="K63" s="88">
+        <v/>
+      </c>
+      <c r="K63" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1204.1882745911005</v>
-      </c>
-      <c r="L63" s="88">
+        <v/>
+      </c>
+      <c r="L63" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M63" s="88">
+        <v/>
+      </c>
+      <c r="M63" s="88" t="str">
         <f>IF(OR($B64=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N63" s="84"/>
       <c r="O63" s="84"/>
-      <c r="P63" s="88">
+      <c r="P63" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B64" s="92">
+      <c r="B64" s="92" t="str">
         <f>IF($B63=Cáratula!$G$35,$B$21,IF(OR($B63="",$B63=$B$21),"",$B63+1))</f>
-        <v>42</v>
-      </c>
-      <c r="C64" s="77">
+        <v/>
+      </c>
+      <c r="C64" s="77" t="str">
         <f>IF(OR($B65=""),$B65,IF(DAY(EOMONTH($C63,1))&lt;Cáratula!$D$69,EOMONTH($C63,1),DATE(YEAR(EOMONTH($C63,1)),MONTH(EOMONTH($C63,1)),Cáratula!$D$69)))</f>
-        <v>47467</v>
-      </c>
-      <c r="D64" s="76">
+        <v/>
+      </c>
+      <c r="D64" s="76" t="str">
         <f>IF(OR($B65=""),"",$C64-Cáratula!$G$38)</f>
-        <v>1249</v>
-      </c>
-      <c r="E64" s="76">
+        <v/>
+      </c>
+      <c r="E64" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F64" s="79">
+        <v/>
+      </c>
+      <c r="F64" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>44913.882778212363</v>
-      </c>
-      <c r="G64" s="79">
+        <v/>
+      </c>
+      <c r="G64" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>43709.694503621264</v>
-      </c>
-      <c r="H64" s="80">
+        <v/>
+      </c>
+      <c r="H64" s="80" t="str">
         <f>IF(OR($B65=""),$B65,(Cáratula!$K$39/365*E64))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I64" s="79">
+        <v/>
+      </c>
+      <c r="I64" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>381.45539684765521</v>
-      </c>
-      <c r="J64" s="82">
+        <v/>
+      </c>
+      <c r="J64" s="82" t="str">
         <f>IF(OR($B65=""),"",IF(C62="",Cáratula!$P$40*E64*G63,Cáratula!$P$40*E64*G64))</f>
-        <v>33.066084510520284</v>
-      </c>
-      <c r="K64" s="82">
+        <v/>
+      </c>
+      <c r="K64" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1229.806257685231</v>
-      </c>
-      <c r="L64" s="82">
+        <v/>
+      </c>
+      <c r="L64" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M64" s="82">
+        <v/>
+      </c>
+      <c r="M64" s="82" t="str">
         <f>IF(OR($B65=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N64" s="76"/>
       <c r="O64" s="76"/>
-      <c r="P64" s="82">
+      <c r="P64" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B65" s="91">
+      <c r="B65" s="91" t="str">
         <f>IF($B64=Cáratula!$G$35,$B$21,IF(OR($B64="",$B64=$B$21),"",$B64+1))</f>
-        <v>43</v>
-      </c>
-      <c r="C65" s="85">
+        <v/>
+      </c>
+      <c r="C65" s="85" t="str">
         <f>IF(OR($B66=""),$B66,IF(DAY(EOMONTH($C64,1))&lt;Cáratula!$D$69,EOMONTH($C64,1),DATE(YEAR(EOMONTH($C64,1)),MONTH(EOMONTH($C64,1)),Cáratula!$D$69)))</f>
-        <v>47498</v>
-      </c>
-      <c r="D65" s="84">
+        <v/>
+      </c>
+      <c r="D65" s="84" t="str">
         <f>IF(OR($B66=""),"",$C65-Cáratula!$G$38)</f>
-        <v>1280</v>
-      </c>
-      <c r="E65" s="84">
+        <v/>
+      </c>
+      <c r="E65" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F65" s="86">
+        <v/>
+      </c>
+      <c r="F65" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>43709.694503621264</v>
-      </c>
-      <c r="G65" s="86">
+        <v/>
+      </c>
+      <c r="G65" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>42479.888245936032</v>
-      </c>
-      <c r="H65" s="87">
+        <v/>
+      </c>
+      <c r="H65" s="87" t="str">
         <f>IF(OR($B66=""),$B66,(Cáratula!$K$39/365*E65))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I65" s="86">
+        <v/>
+      </c>
+      <c r="I65" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>383.08028093112364</v>
-      </c>
-      <c r="J65" s="88">
+        <v/>
+      </c>
+      <c r="J65" s="88" t="str">
         <f>IF(OR($B66=""),"",IF(C63="",Cáratula!$P$40*E65*G64,Cáratula!$P$40*E65*G65))</f>
-        <v>33.206935983242332</v>
-      </c>
-      <c r="K65" s="88">
+        <v/>
+      </c>
+      <c r="K65" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1228.0405221290405</v>
-      </c>
-      <c r="L65" s="88">
+        <v/>
+      </c>
+      <c r="L65" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M65" s="88">
+        <v/>
+      </c>
+      <c r="M65" s="88" t="str">
         <f>IF(OR($B66=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N65" s="84"/>
       <c r="O65" s="84"/>
-      <c r="P65" s="88">
+      <c r="P65" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B66" s="92">
+      <c r="B66" s="92" t="str">
         <f>IF($B65=Cáratula!$G$35,$B$21,IF(OR($B65="",$B65=$B$21),"",$B65+1))</f>
-        <v>44</v>
-      </c>
-      <c r="C66" s="77">
+        <v/>
+      </c>
+      <c r="C66" s="77" t="str">
         <f>IF(OR($B67=""),$B67,IF(DAY(EOMONTH($C65,1))&lt;Cáratula!$D$69,EOMONTH($C65,1),DATE(YEAR(EOMONTH($C65,1)),MONTH(EOMONTH($C65,1)),Cáratula!$D$69)))</f>
-        <v>47529</v>
-      </c>
-      <c r="D66" s="76">
+        <v/>
+      </c>
+      <c r="D66" s="76" t="str">
         <f>IF(OR($B67=""),"",$C66-Cáratula!$G$38)</f>
-        <v>1311</v>
-      </c>
-      <c r="E66" s="76">
+        <v/>
+      </c>
+      <c r="E66" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F66" s="79">
+        <v/>
+      </c>
+      <c r="F66" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>42479.888245936032</v>
-      </c>
-      <c r="G66" s="79">
+        <v/>
+      </c>
+      <c r="G66" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>41251.84772380699</v>
-      </c>
-      <c r="H66" s="80">
+        <v/>
+      </c>
+      <c r="H66" s="80" t="str">
         <f>IF(OR($B67=""),$B67,(Cáratula!$K$39/365*E66))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I66" s="79">
+        <v/>
+      </c>
+      <c r="I66" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>372.00590838361575</v>
-      </c>
-      <c r="J66" s="82">
+        <v/>
+      </c>
+      <c r="J66" s="82" t="str">
         <f>IF(OR($B67=""),"",IF(C64="",Cáratula!$P$40*E66*G65,Cáratula!$P$40*E66*G66))</f>
-        <v>32.246964931363024</v>
-      </c>
-      <c r="K66" s="82">
+        <v/>
+      </c>
+      <c r="K66" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1240.074865728428</v>
-      </c>
-      <c r="L66" s="82">
+        <v/>
+      </c>
+      <c r="L66" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M66" s="82">
+        <v/>
+      </c>
+      <c r="M66" s="82" t="str">
         <f>IF(OR($B67=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N66" s="76"/>
       <c r="O66" s="76"/>
-      <c r="P66" s="82">
+      <c r="P66" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B67" s="91">
+      <c r="B67" s="91" t="str">
         <f>IF($B66=Cáratula!$G$35,$B$21,IF(OR($B66="",$B66=$B$21),"",$B66+1))</f>
-        <v>45</v>
-      </c>
-      <c r="C67" s="85">
+        <v/>
+      </c>
+      <c r="C67" s="85" t="str">
         <f>IF(OR($B68=""),$B68,IF(DAY(EOMONTH($C66,1))&lt;Cáratula!$D$69,EOMONTH($C66,1),DATE(YEAR(EOMONTH($C66,1)),MONTH(EOMONTH($C66,1)),Cáratula!$D$69)))</f>
-        <v>47557</v>
-      </c>
-      <c r="D67" s="84">
+        <v/>
+      </c>
+      <c r="D67" s="84" t="str">
         <f>IF(OR($B68=""),"",$C67-Cáratula!$G$38)</f>
-        <v>1339</v>
-      </c>
-      <c r="E67" s="84">
+        <v/>
+      </c>
+      <c r="E67" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>28</v>
-      </c>
-      <c r="F67" s="86">
+        <v/>
+      </c>
+      <c r="F67" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>41251.84772380699</v>
-      </c>
-      <c r="G67" s="86">
+        <v/>
+      </c>
+      <c r="G67" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>40011.772858078562</v>
-      </c>
-      <c r="H67" s="87">
+        <v/>
+      </c>
+      <c r="H67" s="87" t="str">
         <f>IF(OR($B68=""),$B68,(Cáratula!$K$39/365*E67))</f>
-        <v>8.1452190664090662E-3</v>
-      </c>
-      <c r="I67" s="86">
+        <v/>
+      </c>
+      <c r="I67" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>325.90465516445028</v>
-      </c>
-      <c r="J67" s="88">
+        <v/>
+      </c>
+      <c r="J67" s="88" t="str">
         <f>IF(OR($B68=""),"",IF(C65="",Cáratula!$P$40*E67*G66,Cáratula!$P$40*E67*G67))</f>
-        <v>28.250723306304501</v>
-      </c>
-      <c r="K67" s="88">
+        <v/>
+      </c>
+      <c r="K67" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1290.1723605726518</v>
-      </c>
-      <c r="L67" s="88">
+        <v/>
+      </c>
+      <c r="L67" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M67" s="88">
+        <v/>
+      </c>
+      <c r="M67" s="88" t="str">
         <f>IF(OR($B68=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N67" s="84"/>
       <c r="O67" s="84"/>
-      <c r="P67" s="88">
+      <c r="P67" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B68" s="92">
+      <c r="B68" s="92" t="str">
         <f>IF($B67=Cáratula!$G$35,$B$21,IF(OR($B67="",$B67=$B$21),"",$B67+1))</f>
-        <v>46</v>
-      </c>
-      <c r="C68" s="77">
+        <v/>
+      </c>
+      <c r="C68" s="77" t="str">
         <f>IF(OR($B69=""),$B69,IF(DAY(EOMONTH($C67,1))&lt;Cáratula!$D$69,EOMONTH($C67,1),DATE(YEAR(EOMONTH($C67,1)),MONTH(EOMONTH($C67,1)),Cáratula!$D$69)))</f>
-        <v>47588</v>
-      </c>
-      <c r="D68" s="76">
+        <v/>
+      </c>
+      <c r="D68" s="76" t="str">
         <f>IF(OR($B69=""),"",$C68-Cáratula!$G$38)</f>
-        <v>1370</v>
-      </c>
-      <c r="E68" s="76">
+        <v/>
+      </c>
+      <c r="E68" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F68" s="79">
+        <v/>
+      </c>
+      <c r="F68" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>40011.772858078562</v>
-      </c>
-      <c r="G68" s="79">
+        <v/>
+      </c>
+      <c r="G68" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>38721.600497505911</v>
-      </c>
-      <c r="H68" s="80">
+        <v/>
+      </c>
+      <c r="H68" s="80" t="str">
         <f>IF(OR($B69=""),$B69,(Cáratula!$K$39/365*E68))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I68" s="79">
+        <v/>
+      </c>
+      <c r="I68" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>349.18833850996282</v>
-      </c>
-      <c r="J68" s="82">
+        <v/>
+      </c>
+      <c r="J68" s="82" t="str">
         <f>IF(OR($B69=""),"",IF(C66="",Cáratula!$P$40*E68*G67,Cáratula!$P$40*E68*G68))</f>
-        <v>30.26904641191884</v>
-      </c>
-      <c r="K68" s="82">
+        <v/>
+      </c>
+      <c r="K68" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1264.8703541215248</v>
-      </c>
-      <c r="L68" s="82">
+        <v/>
+      </c>
+      <c r="L68" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M68" s="82">
+        <v/>
+      </c>
+      <c r="M68" s="82" t="str">
         <f>IF(OR($B69=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N68" s="76"/>
       <c r="O68" s="76"/>
-      <c r="P68" s="82">
+      <c r="P68" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B69" s="91">
+      <c r="B69" s="91" t="str">
         <f>IF($B68=Cáratula!$G$35,$B$21,IF(OR($B68="",$B68=$B$21),"",$B68+1))</f>
-        <v>47</v>
-      </c>
-      <c r="C69" s="85">
+        <v/>
+      </c>
+      <c r="C69" s="85" t="str">
         <f>IF(OR($B70=""),$B70,IF(DAY(EOMONTH($C68,1))&lt;Cáratula!$D$69,EOMONTH($C68,1),DATE(YEAR(EOMONTH($C68,1)),MONTH(EOMONTH($C68,1)),Cáratula!$D$69)))</f>
-        <v>47618</v>
-      </c>
-      <c r="D69" s="84">
+        <v/>
+      </c>
+      <c r="D69" s="84" t="str">
         <f>IF(OR($B70=""),"",$C69-Cáratula!$G$38)</f>
-        <v>1400</v>
-      </c>
-      <c r="E69" s="84">
+        <v/>
+      </c>
+      <c r="E69" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F69" s="86">
+        <v/>
+      </c>
+      <c r="F69" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>38721.600497505911</v>
-      </c>
-      <c r="G69" s="86">
+        <v/>
+      </c>
+      <c r="G69" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>37456.73014338439</v>
-      </c>
-      <c r="H69" s="87">
+        <v/>
+      </c>
+      <c r="H69" s="87" t="str">
         <f>IF(OR($B70=""),$B70,(Cáratula!$K$39/365*E69))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I69" s="86">
+        <v/>
+      </c>
+      <c r="I69" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>326.88564913846471</v>
-      </c>
-      <c r="J69" s="88">
+        <v/>
+      </c>
+      <c r="J69" s="88" t="str">
         <f>IF(OR($B70=""),"",IF(C67="",Cáratula!$P$40*E69*G68,Cáratula!$P$40*E69*G69))</f>
-        <v>28.335759800524102</v>
-      </c>
-      <c r="K69" s="88">
+        <v/>
+      </c>
+      <c r="K69" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1289.1063301044178</v>
-      </c>
-      <c r="L69" s="88">
+        <v/>
+      </c>
+      <c r="L69" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M69" s="88">
+        <v/>
+      </c>
+      <c r="M69" s="88" t="str">
         <f>IF(OR($B70=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N69" s="84"/>
       <c r="O69" s="84"/>
-      <c r="P69" s="88">
+      <c r="P69" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B70" s="92">
+      <c r="B70" s="92" t="str">
         <f>IF($B69=Cáratula!$G$35,$B$21,IF(OR($B69="",$B69=$B$21),"",$B69+1))</f>
-        <v>48</v>
-      </c>
-      <c r="C70" s="77">
+        <v/>
+      </c>
+      <c r="C70" s="77" t="str">
         <f>IF(OR($B71=""),$B71,IF(DAY(EOMONTH($C69,1))&lt;Cáratula!$D$69,EOMONTH($C69,1),DATE(YEAR(EOMONTH($C69,1)),MONTH(EOMONTH($C69,1)),Cáratula!$D$69)))</f>
-        <v>47649</v>
-      </c>
-      <c r="D70" s="76">
+        <v/>
+      </c>
+      <c r="D70" s="76" t="str">
         <f>IF(OR($B71=""),"",$C70-Cáratula!$G$38)</f>
-        <v>1431</v>
-      </c>
-      <c r="E70" s="76">
+        <v/>
+      </c>
+      <c r="E70" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F70" s="79">
+        <v/>
+      </c>
+      <c r="F70" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>37456.73014338439</v>
-      </c>
-      <c r="G70" s="79">
+        <v/>
+      </c>
+      <c r="G70" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>36167.62381327997</v>
-      </c>
-      <c r="H70" s="80">
+        <v/>
+      </c>
+      <c r="H70" s="80" t="str">
         <f>IF(OR($B71=""),$B71,(Cáratula!$K$39/365*E70))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I70" s="79">
+        <v/>
+      </c>
+      <c r="I70" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>326.15677825677847</v>
-      </c>
-      <c r="J70" s="82">
+        <v/>
+      </c>
+      <c r="J70" s="82" t="str">
         <f>IF(OR($B71=""),"",IF(C68="",Cáratula!$P$40*E70*G69,Cáratula!$P$40*E70*G70))</f>
-        <v>28.272578347672038</v>
-      </c>
-      <c r="K70" s="82">
+        <v/>
+      </c>
+      <c r="K70" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1289.8983824389561</v>
-      </c>
-      <c r="L70" s="82">
+        <v/>
+      </c>
+      <c r="L70" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M70" s="82">
+        <v/>
+      </c>
+      <c r="M70" s="82" t="str">
         <f>IF(OR($B71=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N70" s="76"/>
       <c r="O70" s="76"/>
-      <c r="P70" s="82">
+      <c r="P70" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B71" s="91">
+      <c r="B71" s="91" t="str">
         <f>IF($B70=Cáratula!$G$35,$B$21,IF(OR($B70="",$B70=$B$21),"",$B70+1))</f>
-        <v>49</v>
-      </c>
-      <c r="C71" s="85">
+        <v/>
+      </c>
+      <c r="C71" s="85" t="str">
         <f>IF(OR($B72=""),$B72,IF(DAY(EOMONTH($C70,1))&lt;Cáratula!$D$69,EOMONTH($C70,1),DATE(YEAR(EOMONTH($C70,1)),MONTH(EOMONTH($C70,1)),Cáratula!$D$69)))</f>
-        <v>47679</v>
-      </c>
-      <c r="D71" s="84">
+        <v/>
+      </c>
+      <c r="D71" s="84" t="str">
         <f>IF(OR($B72=""),"",$C71-Cáratula!$G$38)</f>
-        <v>1461</v>
-      </c>
-      <c r="E71" s="84">
+        <v/>
+      </c>
+      <c r="E71" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F71" s="86">
+        <v/>
+      </c>
+      <c r="F71" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>36167.62381327997</v>
-      </c>
-      <c r="G71" s="86">
+        <v/>
+      </c>
+      <c r="G71" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>34877.725430841012</v>
-      </c>
-      <c r="H71" s="87">
+        <v/>
+      </c>
+      <c r="H71" s="87" t="str">
         <f>IF(OR($B72=""),$B72,(Cáratula!$K$39/365*E71))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I71" s="86">
+        <v/>
+      </c>
+      <c r="I71" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>304.3786223274285</v>
-      </c>
-      <c r="J71" s="88">
+        <v/>
+      </c>
+      <c r="J71" s="88" t="str">
         <f>IF(OR($B72=""),"",IF(C69="",Cáratula!$P$40*E71*G70,Cáratula!$P$40*E71*G71))</f>
-        <v>26.384760399900877</v>
-      </c>
-      <c r="K71" s="88">
+        <v/>
+      </c>
+      <c r="K71" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1313.5643563160772</v>
-      </c>
-      <c r="L71" s="88">
+        <v/>
+      </c>
+      <c r="L71" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M71" s="88">
+        <v/>
+      </c>
+      <c r="M71" s="88" t="str">
         <f>IF(OR($B72=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N71" s="84"/>
       <c r="O71" s="84"/>
-      <c r="P71" s="88">
+      <c r="P71" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B72" s="92">
+      <c r="B72" s="92" t="str">
         <f>IF($B71=Cáratula!$G$35,$B$21,IF(OR($B71="",$B71=$B$21),"",$B71+1))</f>
-        <v>50</v>
-      </c>
-      <c r="C72" s="77">
+        <v/>
+      </c>
+      <c r="C72" s="77" t="str">
         <f>IF(OR($B73=""),$B73,IF(DAY(EOMONTH($C71,1))&lt;Cáratula!$D$69,EOMONTH($C71,1),DATE(YEAR(EOMONTH($C71,1)),MONTH(EOMONTH($C71,1)),Cáratula!$D$69)))</f>
-        <v>47710</v>
-      </c>
-      <c r="D72" s="76">
+        <v/>
+      </c>
+      <c r="D72" s="76" t="str">
         <f>IF(OR($B73=""),"",$C72-Cáratula!$G$38)</f>
-        <v>1492</v>
-      </c>
-      <c r="E72" s="76">
+        <v/>
+      </c>
+      <c r="E72" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F72" s="79">
+        <v/>
+      </c>
+      <c r="F72" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>34877.725430841012</v>
-      </c>
-      <c r="G72" s="79">
+        <v/>
+      </c>
+      <c r="G72" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>33564.161074524935</v>
-      </c>
-      <c r="H72" s="80">
+        <v/>
+      </c>
+      <c r="H72" s="80" t="str">
         <f>IF(OR($B73=""),$B73,(Cáratula!$K$39/365*E72))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I72" s="79">
+        <v/>
+      </c>
+      <c r="I72" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>302.67895666784324</v>
-      </c>
-      <c r="J72" s="82">
+        <v/>
+      </c>
+      <c r="J72" s="82" t="str">
         <f>IF(OR($B73=""),"",IF(C70="",Cáratula!$P$40*E72*G71,Cáratula!$P$40*E72*G72))</f>
-        <v>26.237426560076031</v>
-      </c>
-      <c r="K72" s="82">
+        <v/>
+      </c>
+      <c r="K72" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1315.4113558154872</v>
-      </c>
-      <c r="L72" s="82">
+        <v/>
+      </c>
+      <c r="L72" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M72" s="82">
+        <v/>
+      </c>
+      <c r="M72" s="82" t="str">
         <f>IF(OR($B73=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N72" s="76"/>
       <c r="O72" s="76"/>
-      <c r="P72" s="82">
+      <c r="P72" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="91">
+      <c r="B73" s="91" t="str">
         <f>IF($B72=Cáratula!$G$35,$B$21,IF(OR($B72="",$B72=$B$21),"",$B72+1))</f>
-        <v>51</v>
-      </c>
-      <c r="C73" s="85">
+        <v/>
+      </c>
+      <c r="C73" s="85" t="str">
         <f>IF(OR($B74=""),$B74,IF(DAY(EOMONTH($C72,1))&lt;Cáratula!$D$69,EOMONTH($C72,1),DATE(YEAR(EOMONTH($C72,1)),MONTH(EOMONTH($C72,1)),Cáratula!$D$69)))</f>
-        <v>47741</v>
-      </c>
-      <c r="D73" s="84">
+        <v/>
+      </c>
+      <c r="D73" s="84" t="str">
         <f>IF(OR($B74=""),"",$C73-Cáratula!$G$38)</f>
-        <v>1523</v>
-      </c>
-      <c r="E73" s="84">
+        <v/>
+      </c>
+      <c r="E73" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F73" s="86">
+        <v/>
+      </c>
+      <c r="F73" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>33564.161074524935</v>
-      </c>
-      <c r="G73" s="86">
+        <v/>
+      </c>
+      <c r="G73" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>32248.749718709449</v>
-      </c>
-      <c r="H73" s="87">
+        <v/>
+      </c>
+      <c r="H73" s="87" t="str">
         <f>IF(OR($B74=""),$B74,(Cáratula!$K$39/365*E73))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I73" s="86">
+        <v/>
+      </c>
+      <c r="I73" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>290.81668083490263</v>
-      </c>
-      <c r="J73" s="88">
+        <v/>
+      </c>
+      <c r="J73" s="88" t="str">
         <f>IF(OR($B74=""),"",IF(C71="",Cáratula!$P$40*E73*G72,Cáratula!$P$40*E73*G73))</f>
-        <v>25.209156889701518</v>
-      </c>
-      <c r="K73" s="88">
+        <v/>
+      </c>
+      <c r="K73" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1328.3019013188025</v>
-      </c>
-      <c r="L73" s="88">
+        <v/>
+      </c>
+      <c r="L73" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M73" s="88">
+        <v/>
+      </c>
+      <c r="M73" s="88" t="str">
         <f>IF(OR($B74=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N73" s="84"/>
       <c r="O73" s="84"/>
-      <c r="P73" s="88">
+      <c r="P73" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B74" s="92">
+      <c r="B74" s="92" t="str">
         <f>IF($B73=Cáratula!$G$35,$B$21,IF(OR($B73="",$B73=$B$21),"",$B73+1))</f>
-        <v>52</v>
-      </c>
-      <c r="C74" s="77">
+        <v/>
+      </c>
+      <c r="C74" s="77" t="str">
         <f>IF(OR($B75=""),$B75,IF(DAY(EOMONTH($C73,1))&lt;Cáratula!$D$69,EOMONTH($C73,1),DATE(YEAR(EOMONTH($C73,1)),MONTH(EOMONTH($C73,1)),Cáratula!$D$69)))</f>
-        <v>47771</v>
-      </c>
-      <c r="D74" s="76">
+        <v/>
+      </c>
+      <c r="D74" s="76" t="str">
         <f>IF(OR($B75=""),"",$C74-Cáratula!$G$38)</f>
-        <v>1553</v>
-      </c>
-      <c r="E74" s="76">
+        <v/>
+      </c>
+      <c r="E74" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F74" s="79">
+        <v/>
+      </c>
+      <c r="F74" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>32248.749718709449</v>
-      </c>
-      <c r="G74" s="79">
+        <v/>
+      </c>
+      <c r="G74" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>30920.447817390646</v>
-      </c>
-      <c r="H74" s="80">
+        <v/>
+      </c>
+      <c r="H74" s="80" t="str">
         <f>IF(OR($B75=""),$B75,(Cáratula!$K$39/365*E74))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I74" s="79">
+        <v/>
+      </c>
+      <c r="I74" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>269.84337975441099</v>
-      </c>
-      <c r="J74" s="82">
+        <v/>
+      </c>
+      <c r="J74" s="82" t="str">
         <f>IF(OR($B75=""),"",IF(C72="",Cáratula!$P$40*E74*G73,Cáratula!$P$40*E74*G74))</f>
-        <v>23.391106989966861</v>
-      </c>
-      <c r="K74" s="82">
+        <v/>
+      </c>
+      <c r="K74" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1351.0932522990288</v>
-      </c>
-      <c r="L74" s="82">
+        <v/>
+      </c>
+      <c r="L74" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M74" s="82">
+        <v/>
+      </c>
+      <c r="M74" s="82" t="str">
         <f>IF(OR($B75=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N74" s="76"/>
       <c r="O74" s="76"/>
-      <c r="P74" s="82">
+      <c r="P74" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B75" s="91">
+      <c r="B75" s="91" t="str">
         <f>IF($B74=Cáratula!$G$35,$B$21,IF(OR($B74="",$B74=$B$21),"",$B74+1))</f>
-        <v>53</v>
-      </c>
-      <c r="C75" s="85">
+        <v/>
+      </c>
+      <c r="C75" s="85" t="str">
         <f>IF(OR($B76=""),$B76,IF(DAY(EOMONTH($C74,1))&lt;Cáratula!$D$69,EOMONTH($C74,1),DATE(YEAR(EOMONTH($C74,1)),MONTH(EOMONTH($C74,1)),Cáratula!$D$69)))</f>
-        <v>47802</v>
-      </c>
-      <c r="D75" s="84">
+        <v/>
+      </c>
+      <c r="D75" s="84" t="str">
         <f>IF(OR($B76=""),"",$C75-Cáratula!$G$38)</f>
-        <v>1584</v>
-      </c>
-      <c r="E75" s="84">
+        <v/>
+      </c>
+      <c r="E75" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F75" s="86">
+        <v/>
+      </c>
+      <c r="F75" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>30920.447817390646</v>
-      </c>
-      <c r="G75" s="86">
+        <v/>
+      </c>
+      <c r="G75" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>29569.354565091617</v>
-      </c>
-      <c r="H75" s="87">
+        <v/>
+      </c>
+      <c r="H75" s="87" t="str">
         <f>IF(OR($B76=""),$B76,(Cáratula!$K$39/365*E75))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I75" s="86">
+        <v/>
+      </c>
+      <c r="I75" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>266.65410671910075</v>
-      </c>
-      <c r="J75" s="88">
+        <v/>
+      </c>
+      <c r="J75" s="88" t="str">
         <f>IF(OR($B76=""),"",IF(C73="",Cáratula!$P$40*E75*G74,Cáratula!$P$40*E75*G75))</f>
-        <v>23.11464800528822</v>
-      </c>
-      <c r="K75" s="88">
+        <v/>
+      </c>
+      <c r="K75" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1354.5589843190176</v>
-      </c>
-      <c r="L75" s="88">
+        <v/>
+      </c>
+      <c r="L75" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M75" s="88">
+        <v/>
+      </c>
+      <c r="M75" s="88" t="str">
         <f>IF(OR($B76=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N75" s="84"/>
       <c r="O75" s="84"/>
-      <c r="P75" s="88">
+      <c r="P75" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B76" s="92">
+      <c r="B76" s="92" t="str">
         <f>IF($B75=Cáratula!$G$35,$B$21,IF(OR($B75="",$B75=$B$21),"",$B75+1))</f>
-        <v>54</v>
-      </c>
-      <c r="C76" s="77">
+        <v/>
+      </c>
+      <c r="C76" s="77" t="str">
         <f>IF(OR($B77=""),$B77,IF(DAY(EOMONTH($C75,1))&lt;Cáratula!$D$69,EOMONTH($C75,1),DATE(YEAR(EOMONTH($C75,1)),MONTH(EOMONTH($C75,1)),Cáratula!$D$69)))</f>
-        <v>47832</v>
-      </c>
-      <c r="D76" s="76">
+        <v/>
+      </c>
+      <c r="D76" s="76" t="str">
         <f>IF(OR($B77=""),"",$C76-Cáratula!$G$38)</f>
-        <v>1614</v>
-      </c>
-      <c r="E76" s="76">
+        <v/>
+      </c>
+      <c r="E76" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F76" s="79">
+        <v/>
+      </c>
+      <c r="F76" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>29569.354565091617</v>
-      </c>
-      <c r="G76" s="79">
+        <v/>
+      </c>
+      <c r="G76" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>28214.795580772599</v>
-      </c>
-      <c r="H76" s="80">
+        <v/>
+      </c>
+      <c r="H76" s="80" t="str">
         <f>IF(OR($B77=""),$B77,(Cáratula!$K$39/365*E76))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I76" s="79">
+        <v/>
+      </c>
+      <c r="I76" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>246.23109741358206</v>
-      </c>
-      <c r="J76" s="82">
+        <v/>
+      </c>
+      <c r="J76" s="82" t="str">
         <f>IF(OR($B77=""),"",IF(C74="",Cáratula!$P$40*E76*G75,Cáratula!$P$40*E76*G76))</f>
-        <v>21.344299604829946</v>
-      </c>
-      <c r="K76" s="82">
+        <v/>
+      </c>
+      <c r="K76" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1376.7523420249945</v>
-      </c>
-      <c r="L76" s="82">
+        <v/>
+      </c>
+      <c r="L76" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M76" s="82">
+        <v/>
+      </c>
+      <c r="M76" s="82" t="str">
         <f>IF(OR($B77=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N76" s="76"/>
       <c r="O76" s="76"/>
-      <c r="P76" s="82">
+      <c r="P76" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B77" s="91">
+      <c r="B77" s="91" t="str">
         <f>IF($B76=Cáratula!$G$35,$B$21,IF(OR($B76="",$B76=$B$21),"",$B76+1))</f>
-        <v>55</v>
-      </c>
-      <c r="C77" s="85">
+        <v/>
+      </c>
+      <c r="C77" s="85" t="str">
         <f>IF(OR($B78=""),$B78,IF(DAY(EOMONTH($C76,1))&lt;Cáratula!$D$69,EOMONTH($C76,1),DATE(YEAR(EOMONTH($C76,1)),MONTH(EOMONTH($C76,1)),Cáratula!$D$69)))</f>
-        <v>47863</v>
-      </c>
-      <c r="D77" s="84">
+        <v/>
+      </c>
+      <c r="D77" s="84" t="str">
         <f>IF(OR($B78=""),"",$C77-Cáratula!$G$38)</f>
-        <v>1645</v>
-      </c>
-      <c r="E77" s="84">
+        <v/>
+      </c>
+      <c r="E77" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F77" s="86">
+        <v/>
+      </c>
+      <c r="F77" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>28214.795580772599</v>
-      </c>
-      <c r="G77" s="86">
+        <v/>
+      </c>
+      <c r="G77" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>26838.043238747603</v>
-      </c>
-      <c r="H77" s="87">
+        <v/>
+      </c>
+      <c r="H77" s="87" t="str">
         <f>IF(OR($B78=""),$B78,(Cáratula!$K$39/365*E77))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I77" s="86">
+        <v/>
+      </c>
+      <c r="I77" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>242.02335665336054</v>
-      </c>
-      <c r="J77" s="88">
+        <v/>
+      </c>
+      <c r="J77" s="88" t="str">
         <f>IF(OR($B78=""),"",IF(C75="",Cáratula!$P$40*E77*G76,Cáratula!$P$40*E77*G77))</f>
-        <v>20.979555750828549</v>
-      </c>
-      <c r="K77" s="88">
+        <v/>
+      </c>
+      <c r="K77" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1381.3248266392177</v>
-      </c>
-      <c r="L77" s="88">
+        <v/>
+      </c>
+      <c r="L77" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M77" s="88">
+        <v/>
+      </c>
+      <c r="M77" s="88" t="str">
         <f>IF(OR($B78=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N77" s="84"/>
       <c r="O77" s="84"/>
-      <c r="P77" s="88">
+      <c r="P77" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B78" s="92">
+      <c r="B78" s="92" t="str">
         <f>IF($B77=Cáratula!$G$35,$B$21,IF(OR($B77="",$B77=$B$21),"",$B77+1))</f>
-        <v>56</v>
-      </c>
-      <c r="C78" s="77">
+        <v/>
+      </c>
+      <c r="C78" s="77" t="str">
         <f>IF(OR($B79=""),$B79,IF(DAY(EOMONTH($C77,1))&lt;Cáratula!$D$69,EOMONTH($C77,1),DATE(YEAR(EOMONTH($C77,1)),MONTH(EOMONTH($C77,1)),Cáratula!$D$69)))</f>
-        <v>47894</v>
-      </c>
-      <c r="D78" s="76">
+        <v/>
+      </c>
+      <c r="D78" s="76" t="str">
         <f>IF(OR($B79=""),"",$C78-Cáratula!$G$38)</f>
-        <v>1676</v>
-      </c>
-      <c r="E78" s="76">
+        <v/>
+      </c>
+      <c r="E78" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F78" s="79">
+        <v/>
+      </c>
+      <c r="F78" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>26838.043238747603</v>
-      </c>
-      <c r="G78" s="79">
+        <v/>
+      </c>
+      <c r="G78" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>25456.718412108385</v>
-      </c>
-      <c r="H78" s="80">
+        <v/>
+      </c>
+      <c r="H78" s="80" t="str">
         <f>IF(OR($B79=""),$B79,(Cáratula!$K$39/365*E78))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I78" s="79">
+        <v/>
+      </c>
+      <c r="I78" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>229.56667834049537</v>
-      </c>
-      <c r="J78" s="82">
+        <v/>
+      </c>
+      <c r="J78" s="82" t="str">
         <f>IF(OR($B79=""),"",IF(C76="",Cáratula!$P$40*E78*G77,Cáratula!$P$40*E78*G78))</f>
-        <v>19.899760888264144</v>
-      </c>
-      <c r="K78" s="82">
+        <v/>
+      </c>
+      <c r="K78" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1394.8612998146471</v>
-      </c>
-      <c r="L78" s="82">
+        <v/>
+      </c>
+      <c r="L78" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M78" s="82">
+        <v/>
+      </c>
+      <c r="M78" s="82" t="str">
         <f>IF(OR($B79=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N78" s="76"/>
       <c r="O78" s="76"/>
-      <c r="P78" s="82">
+      <c r="P78" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B79" s="91">
+      <c r="B79" s="91" t="str">
         <f>IF($B78=Cáratula!$G$35,$B$21,IF(OR($B78="",$B78=$B$21),"",$B78+1))</f>
-        <v>57</v>
-      </c>
-      <c r="C79" s="85">
+        <v/>
+      </c>
+      <c r="C79" s="85" t="str">
         <f>IF(OR($B80=""),$B80,IF(DAY(EOMONTH($C78,1))&lt;Cáratula!$D$69,EOMONTH($C78,1),DATE(YEAR(EOMONTH($C78,1)),MONTH(EOMONTH($C78,1)),Cáratula!$D$69)))</f>
-        <v>47922</v>
-      </c>
-      <c r="D79" s="84">
+        <v/>
+      </c>
+      <c r="D79" s="84" t="str">
         <f>IF(OR($B80=""),"",$C79-Cáratula!$G$38)</f>
-        <v>1704</v>
-      </c>
-      <c r="E79" s="84">
+        <v/>
+      </c>
+      <c r="E79" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>28</v>
-      </c>
-      <c r="F79" s="86">
+        <v/>
+      </c>
+      <c r="F79" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>25456.718412108385</v>
-      </c>
-      <c r="G79" s="86">
+        <v/>
+      </c>
+      <c r="G79" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>24061.857112293739</v>
-      </c>
-      <c r="H79" s="87">
+        <v/>
+      </c>
+      <c r="H79" s="87" t="str">
         <f>IF(OR($B80=""),$B80,(Cáratula!$K$39/365*E79))</f>
-        <v>8.1452190664090662E-3</v>
-      </c>
-      <c r="I79" s="86">
+        <v/>
+      </c>
+      <c r="I79" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>195.98909732426557</v>
-      </c>
-      <c r="J79" s="88">
+        <v/>
+      </c>
+      <c r="J79" s="88" t="str">
         <f>IF(OR($B80=""),"",IF(C77="",Cáratula!$P$40*E79*G78,Cáratula!$P$40*E79*G79))</f>
-        <v>16.989121424995737</v>
-      </c>
-      <c r="K79" s="88">
+        <v/>
+      </c>
+      <c r="K79" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1431.3495202941451</v>
-      </c>
-      <c r="L79" s="88">
+        <v/>
+      </c>
+      <c r="L79" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M79" s="88">
+        <v/>
+      </c>
+      <c r="M79" s="88" t="str">
         <f>IF(OR($B80=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N79" s="84"/>
       <c r="O79" s="84"/>
-      <c r="P79" s="88">
+      <c r="P79" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B80" s="92">
+      <c r="B80" s="92" t="str">
         <f>IF($B79=Cáratula!$G$35,$B$21,IF(OR($B79="",$B79=$B$21),"",$B79+1))</f>
-        <v>58</v>
-      </c>
-      <c r="C80" s="77">
+        <v/>
+      </c>
+      <c r="C80" s="77" t="str">
         <f>IF(OR($B81=""),$B81,IF(DAY(EOMONTH($C79,1))&lt;Cáratula!$D$69,EOMONTH($C79,1),DATE(YEAR(EOMONTH($C79,1)),MONTH(EOMONTH($C79,1)),Cáratula!$D$69)))</f>
-        <v>47953</v>
-      </c>
-      <c r="D80" s="76">
+        <v/>
+      </c>
+      <c r="D80" s="76" t="str">
         <f>IF(OR($B81=""),"",$C80-Cáratula!$G$38)</f>
-        <v>1735</v>
-      </c>
-      <c r="E80" s="76">
+        <v/>
+      </c>
+      <c r="E80" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F80" s="79">
+        <v/>
+      </c>
+      <c r="F80" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>24061.857112293739</v>
-      </c>
-      <c r="G80" s="79">
+        <v/>
+      </c>
+      <c r="G80" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>22630.507591999594</v>
-      </c>
-      <c r="H80" s="80">
+        <v/>
+      </c>
+      <c r="H80" s="80" t="str">
         <f>IF(OR($B81=""),$B81,(Cáratula!$K$39/365*E80))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I80" s="79">
+        <v/>
+      </c>
+      <c r="I80" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>204.08013212667774</v>
-      </c>
-      <c r="J80" s="82">
+        <v/>
+      </c>
+      <c r="J80" s="82" t="str">
         <f>IF(OR($B81=""),"",IF(C78="",Cáratula!$P$40*E80*G79,Cáratula!$P$40*E80*G80))</f>
-        <v>17.690484789533404</v>
-      </c>
-      <c r="K80" s="82">
+        <v/>
+      </c>
+      <c r="K80" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1422.5571221271955</v>
-      </c>
-      <c r="L80" s="82">
+        <v/>
+      </c>
+      <c r="L80" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M80" s="82">
+        <v/>
+      </c>
+      <c r="M80" s="82" t="str">
         <f>IF(OR($B81=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N80" s="76"/>
       <c r="O80" s="76"/>
-      <c r="P80" s="82">
+      <c r="P80" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B81" s="91">
+      <c r="B81" s="91" t="str">
         <f>IF($B80=Cáratula!$G$35,$B$21,IF(OR($B80="",$B80=$B$21),"",$B80+1))</f>
-        <v>59</v>
-      </c>
-      <c r="C81" s="85">
+        <v/>
+      </c>
+      <c r="C81" s="85" t="str">
         <f>IF(OR($B82=""),$B82,IF(DAY(EOMONTH($C80,1))&lt;Cáratula!$D$69,EOMONTH($C80,1),DATE(YEAR(EOMONTH($C80,1)),MONTH(EOMONTH($C80,1)),Cáratula!$D$69)))</f>
-        <v>47983</v>
-      </c>
-      <c r="D81" s="84">
+        <v/>
+      </c>
+      <c r="D81" s="84" t="str">
         <f>IF(OR($B82=""),"",$C81-Cáratula!$G$38)</f>
-        <v>1765</v>
-      </c>
-      <c r="E81" s="84">
+        <v/>
+      </c>
+      <c r="E81" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F81" s="86">
+        <v/>
+      </c>
+      <c r="F81" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>22630.507591999594</v>
-      </c>
-      <c r="G81" s="86">
+        <v/>
+      </c>
+      <c r="G81" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>21207.950469872398</v>
-      </c>
-      <c r="H81" s="87">
+        <v/>
+      </c>
+      <c r="H81" s="87" t="str">
         <f>IF(OR($B82=""),$B82,(Cáratula!$K$39/365*E81))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I81" s="86">
+        <v/>
+      </c>
+      <c r="I81" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>185.08221699285406</v>
-      </c>
-      <c r="J81" s="88">
+        <v/>
+      </c>
+      <c r="J81" s="88" t="str">
         <f>IF(OR($B82=""),"",IF(C79="",Cáratula!$P$40*E81*G80,Cáratula!$P$40*E81*G81))</f>
-        <v>16.043669270523743</v>
-      </c>
-      <c r="K81" s="88">
+        <v/>
+      </c>
+      <c r="K81" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1443.201852780029</v>
-      </c>
-      <c r="L81" s="88">
+        <v/>
+      </c>
+      <c r="L81" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M81" s="88">
+        <v/>
+      </c>
+      <c r="M81" s="88" t="str">
         <f>IF(OR($B82=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N81" s="84"/>
       <c r="O81" s="84"/>
-      <c r="P81" s="88">
+      <c r="P81" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B82" s="92">
+      <c r="B82" s="92" t="str">
         <f>IF($B81=Cáratula!$G$35,$B$21,IF(OR($B81="",$B81=$B$21),"",$B81+1))</f>
-        <v>60</v>
-      </c>
-      <c r="C82" s="77">
+        <v/>
+      </c>
+      <c r="C82" s="77" t="str">
         <f>IF(OR($B83=""),$B83,IF(DAY(EOMONTH($C81,1))&lt;Cáratula!$D$69,EOMONTH($C81,1),DATE(YEAR(EOMONTH($C81,1)),MONTH(EOMONTH($C81,1)),Cáratula!$D$69)))</f>
-        <v>48014</v>
-      </c>
-      <c r="D82" s="76">
+        <v/>
+      </c>
+      <c r="D82" s="76" t="str">
         <f>IF(OR($B83=""),"",$C82-Cáratula!$G$38)</f>
-        <v>1796</v>
-      </c>
-      <c r="E82" s="76">
+        <v/>
+      </c>
+      <c r="E82" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F82" s="79">
+        <v/>
+      </c>
+      <c r="F82" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>21207.950469872398</v>
-      </c>
-      <c r="G82" s="79">
+        <v/>
+      </c>
+      <c r="G82" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>19764.748617092369</v>
-      </c>
-      <c r="H82" s="80">
+        <v/>
+      </c>
+      <c r="H82" s="80" t="str">
         <f>IF(OR($B83=""),$B83,(Cáratula!$K$39/365*E82))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I82" s="79">
+        <v/>
+      </c>
+      <c r="I82" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>178.23694377287188</v>
-      </c>
-      <c r="J82" s="82">
+        <v/>
+      </c>
+      <c r="J82" s="82" t="str">
         <f>IF(OR($B83=""),"",IF(C80="",Cáratula!$P$40*E82*G81,Cáratula!$P$40*E82*G82))</f>
-        <v>15.450293518967843</v>
-      </c>
-      <c r="K82" s="82">
+        <v/>
+      </c>
+      <c r="K82" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1450.6405017515669</v>
-      </c>
-      <c r="L82" s="82">
+        <v/>
+      </c>
+      <c r="L82" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M82" s="82">
+        <v/>
+      </c>
+      <c r="M82" s="82" t="str">
         <f>IF(OR($B83=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N82" s="76"/>
       <c r="O82" s="76"/>
-      <c r="P82" s="82">
+      <c r="P82" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B83" s="91">
+      <c r="B83" s="91" t="str">
         <f>IF($B82=Cáratula!$G$35,$B$21,IF(OR($B82="",$B82=$B$21),"",$B82+1))</f>
-        <v>61</v>
-      </c>
-      <c r="C83" s="85">
+        <v/>
+      </c>
+      <c r="C83" s="85" t="str">
         <f>IF(OR($B84=""),$B84,IF(DAY(EOMONTH($C82,1))&lt;Cáratula!$D$69,EOMONTH($C82,1),DATE(YEAR(EOMONTH($C82,1)),MONTH(EOMONTH($C82,1)),Cáratula!$D$69)))</f>
-        <v>48044</v>
-      </c>
-      <c r="D83" s="84">
+        <v/>
+      </c>
+      <c r="D83" s="84" t="str">
         <f>IF(OR($B84=""),"",$C83-Cáratula!$G$38)</f>
-        <v>1826</v>
-      </c>
-      <c r="E83" s="84">
+        <v/>
+      </c>
+      <c r="E83" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F83" s="86">
+        <v/>
+      </c>
+      <c r="F83" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>19764.748617092369</v>
-      </c>
-      <c r="G83" s="86">
+        <v/>
+      </c>
+      <c r="G83" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>18314.108115340801</v>
-      </c>
-      <c r="H83" s="87">
+        <v/>
+      </c>
+      <c r="H83" s="87" t="str">
         <f>IF(OR($B84=""),$B84,(Cáratula!$K$39/365*E83))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I83" s="86">
+        <v/>
+      </c>
+      <c r="I83" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>159.82759564859026</v>
-      </c>
-      <c r="J83" s="88">
+        <v/>
+      </c>
+      <c r="J83" s="88" t="str">
         <f>IF(OR($B84=""),"",IF(C81="",Cáratula!$P$40*E83*G82,Cáratula!$P$40*E83*G83))</f>
-        <v>13.854497350158635</v>
-      </c>
-      <c r="K83" s="88">
+        <v/>
+      </c>
+      <c r="K83" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1470.6456460446577</v>
-      </c>
-      <c r="L83" s="88">
+        <v/>
+      </c>
+      <c r="L83" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M83" s="88">
+        <v/>
+      </c>
+      <c r="M83" s="88" t="str">
         <f>IF(OR($B84=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N83" s="84"/>
       <c r="O83" s="84"/>
-      <c r="P83" s="88">
+      <c r="P83" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B84" s="92">
+      <c r="B84" s="92" t="str">
         <f>IF($B83=Cáratula!$G$35,$B$21,IF(OR($B83="",$B83=$B$21),"",$B83+1))</f>
-        <v>62</v>
-      </c>
-      <c r="C84" s="77">
+        <v/>
+      </c>
+      <c r="C84" s="77" t="str">
         <f>IF(OR($B85=""),$B85,IF(DAY(EOMONTH($C83,1))&lt;Cáratula!$D$69,EOMONTH($C83,1),DATE(YEAR(EOMONTH($C83,1)),MONTH(EOMONTH($C83,1)),Cáratula!$D$69)))</f>
-        <v>48075</v>
-      </c>
-      <c r="D84" s="76">
+        <v/>
+      </c>
+      <c r="D84" s="76" t="str">
         <f>IF(OR($B85=""),"",$C84-Cáratula!$G$38)</f>
-        <v>1857</v>
-      </c>
-      <c r="E84" s="76">
+        <v/>
+      </c>
+      <c r="E84" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F84" s="79">
+        <v/>
+      </c>
+      <c r="F84" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>18314.108115340801</v>
-      </c>
-      <c r="G84" s="79">
+        <v/>
+      </c>
+      <c r="G84" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>16843.462469296144</v>
-      </c>
-      <c r="H84" s="80">
+        <v/>
+      </c>
+      <c r="H84" s="80" t="str">
         <f>IF(OR($B85=""),$B85,(Cáratula!$K$39/365*E84))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I84" s="79">
+        <v/>
+      </c>
+      <c r="I84" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>151.89301575453396</v>
-      </c>
-      <c r="J84" s="82">
+        <v/>
+      </c>
+      <c r="J84" s="82" t="str">
         <f>IF(OR($B85=""),"",IF(C82="",Cáratula!$P$40*E84*G83,Cáratula!$P$40*E84*G84))</f>
-        <v>13.166696124902611</v>
-      </c>
-      <c r="K84" s="82">
+        <v/>
+      </c>
+      <c r="K84" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1479.2680271639701</v>
-      </c>
-      <c r="L84" s="82">
+        <v/>
+      </c>
+      <c r="L84" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M84" s="82">
+        <v/>
+      </c>
+      <c r="M84" s="82" t="str">
         <f>IF(OR($B85=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N84" s="76"/>
       <c r="O84" s="76"/>
-      <c r="P84" s="82">
+      <c r="P84" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B85" s="91">
+      <c r="B85" s="91" t="str">
         <f>IF($B84=Cáratula!$G$35,$B$21,IF(OR($B84="",$B84=$B$21),"",$B84+1))</f>
-        <v>63</v>
-      </c>
-      <c r="C85" s="85">
+        <v/>
+      </c>
+      <c r="C85" s="85" t="str">
         <f>IF(OR($B86=""),$B86,IF(DAY(EOMONTH($C84,1))&lt;Cáratula!$D$69,EOMONTH($C84,1),DATE(YEAR(EOMONTH($C84,1)),MONTH(EOMONTH($C84,1)),Cáratula!$D$69)))</f>
-        <v>48106</v>
-      </c>
-      <c r="D85" s="84">
+        <v/>
+      </c>
+      <c r="D85" s="84" t="str">
         <f>IF(OR($B86=""),"",$C85-Cáratula!$G$38)</f>
-        <v>1888</v>
-      </c>
-      <c r="E85" s="84">
+        <v/>
+      </c>
+      <c r="E85" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F85" s="86">
+        <v/>
+      </c>
+      <c r="F85" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>16843.462469296144</v>
-      </c>
-      <c r="G85" s="86">
+        <v/>
+      </c>
+      <c r="G85" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>15364.194442132175</v>
-      </c>
-      <c r="H85" s="87">
+        <v/>
+      </c>
+      <c r="H85" s="87" t="str">
         <f>IF(OR($B86=""),$B86,(Cáratula!$K$39/365*E85))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I85" s="86">
+        <v/>
+      </c>
+      <c r="I85" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>138.55309338615027</v>
-      </c>
-      <c r="J85" s="88">
+        <v/>
+      </c>
+      <c r="J85" s="88" t="str">
         <f>IF(OR($B86=""),"",IF(C83="",Cáratula!$P$40*E85*G84,Cáratula!$P$40*E85*G85))</f>
-        <v>12.010338123306632</v>
-      </c>
-      <c r="K85" s="88">
+        <v/>
+      </c>
+      <c r="K85" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1493.7643075339497</v>
-      </c>
-      <c r="L85" s="88">
+        <v/>
+      </c>
+      <c r="L85" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M85" s="88">
+        <v/>
+      </c>
+      <c r="M85" s="88" t="str">
         <f>IF(OR($B86=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N85" s="84"/>
       <c r="O85" s="84"/>
-      <c r="P85" s="88">
+      <c r="P85" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B86" s="92">
+      <c r="B86" s="92" t="str">
         <f>IF($B85=Cáratula!$G$35,$B$21,IF(OR($B85="",$B85=$B$21),"",$B85+1))</f>
-        <v>64</v>
-      </c>
-      <c r="C86" s="77">
+        <v/>
+      </c>
+      <c r="C86" s="77" t="str">
         <f>IF(OR($B87=""),$B87,IF(DAY(EOMONTH($C85,1))&lt;Cáratula!$D$69,EOMONTH($C85,1),DATE(YEAR(EOMONTH($C85,1)),MONTH(EOMONTH($C85,1)),Cáratula!$D$69)))</f>
-        <v>48136</v>
-      </c>
-      <c r="D86" s="76">
+        <v/>
+      </c>
+      <c r="D86" s="76" t="str">
         <f>IF(OR($B87=""),"",$C86-Cáratula!$G$38)</f>
-        <v>1918</v>
-      </c>
-      <c r="E86" s="76">
+        <v/>
+      </c>
+      <c r="E86" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F86" s="79">
+        <v/>
+      </c>
+      <c r="F86" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>15364.194442132175</v>
-      </c>
-      <c r="G86" s="79">
+        <v/>
+      </c>
+      <c r="G86" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>13870.430134598226</v>
-      </c>
-      <c r="H86" s="80">
+        <v/>
+      </c>
+      <c r="H86" s="80" t="str">
         <f>IF(OR($B87=""),$B87,(Cáratula!$K$39/365*E86))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I86" s="79">
+        <v/>
+      </c>
+      <c r="I86" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>121.04752713388324</v>
-      </c>
-      <c r="J86" s="82">
+        <v/>
+      </c>
+      <c r="J86" s="82" t="str">
         <f>IF(OR($B87=""),"",IF(C84="",Cáratula!$P$40*E86*G85,Cáratula!$P$40*E86*G86))</f>
-        <v>10.49288539387743</v>
-      </c>
-      <c r="K86" s="82">
+        <v/>
+      </c>
+      <c r="K86" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1512.7873265156459</v>
-      </c>
-      <c r="L86" s="82">
+        <v/>
+      </c>
+      <c r="L86" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M86" s="82">
+        <v/>
+      </c>
+      <c r="M86" s="82" t="str">
         <f>IF(OR($B87=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N86" s="76"/>
       <c r="O86" s="76"/>
-      <c r="P86" s="82">
+      <c r="P86" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B87" s="91">
+      <c r="B87" s="91" t="str">
         <f>IF($B86=Cáratula!$G$35,$B$21,IF(OR($B86="",$B86=$B$21),"",$B86+1))</f>
-        <v>65</v>
-      </c>
-      <c r="C87" s="85">
+        <v/>
+      </c>
+      <c r="C87" s="85" t="str">
         <f>IF(OR($B88=""),$B88,IF(DAY(EOMONTH($C86,1))&lt;Cáratula!$D$69,EOMONTH($C86,1),DATE(YEAR(EOMONTH($C86,1)),MONTH(EOMONTH($C86,1)),Cáratula!$D$69)))</f>
-        <v>48167</v>
-      </c>
-      <c r="D87" s="84">
+        <v/>
+      </c>
+      <c r="D87" s="84" t="str">
         <f>IF(OR($B88=""),"",$C87-Cáratula!$G$38)</f>
-        <v>1949</v>
-      </c>
-      <c r="E87" s="84">
+        <v/>
+      </c>
+      <c r="E87" s="84" t="str">
         <f t="shared" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="F87" s="86">
+        <v/>
+      </c>
+      <c r="F87" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>13870.430134598226</v>
-      </c>
-      <c r="G87" s="86">
+        <v/>
+      </c>
+      <c r="G87" s="86" t="str">
         <f t="shared" si="3"/>
-        <v>12357.642808082579</v>
-      </c>
-      <c r="H87" s="87">
+        <v/>
+      </c>
+      <c r="H87" s="87" t="str">
         <f>IF(OR($B88=""),$B88,(Cáratula!$K$39/365*E87))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I87" s="86">
+        <v/>
+      </c>
+      <c r="I87" s="86" t="str">
         <f t="shared" si="4"/>
-        <v>111.44024793943858</v>
-      </c>
-      <c r="J87" s="88">
+        <v/>
+      </c>
+      <c r="J87" s="88" t="str">
         <f>IF(OR($B88=""),"",IF(C85="",Cáratula!$P$40*E87*G86,Cáratula!$P$40*E87*G87))</f>
-        <v>9.6600878810228874</v>
-      </c>
-      <c r="K87" s="88">
+        <v/>
+      </c>
+      <c r="K87" s="88" t="str">
         <f t="shared" si="5"/>
-        <v>1523.227403222945</v>
-      </c>
-      <c r="L87" s="88">
+        <v/>
+      </c>
+      <c r="L87" s="88" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M87" s="88">
+        <v/>
+      </c>
+      <c r="M87" s="88" t="str">
         <f>IF(OR($B88=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N87" s="84"/>
       <c r="O87" s="84"/>
-      <c r="P87" s="88">
+      <c r="P87" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B88" s="92">
+      <c r="B88" s="92" t="str">
         <f>IF($B87=Cáratula!$G$35,$B$21,IF(OR($B87="",$B87=$B$21),"",$B87+1))</f>
-        <v>66</v>
-      </c>
-      <c r="C88" s="77">
+        <v/>
+      </c>
+      <c r="C88" s="77" t="str">
         <f>IF(OR($B89=""),$B89,IF(DAY(EOMONTH($C87,1))&lt;Cáratula!$D$69,EOMONTH($C87,1),DATE(YEAR(EOMONTH($C87,1)),MONTH(EOMONTH($C87,1)),Cáratula!$D$69)))</f>
-        <v>48197</v>
-      </c>
-      <c r="D88" s="76">
+        <v/>
+      </c>
+      <c r="D88" s="76" t="str">
         <f>IF(OR($B89=""),"",$C88-Cáratula!$G$38)</f>
-        <v>1979</v>
-      </c>
-      <c r="E88" s="76">
+        <v/>
+      </c>
+      <c r="E88" s="76" t="str">
         <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="F88" s="79">
+        <v/>
+      </c>
+      <c r="F88" s="79" t="str">
         <f t="shared" si="8"/>
-        <v>12357.642808082579</v>
-      </c>
-      <c r="G88" s="79">
+        <v/>
+      </c>
+      <c r="G88" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>10834.415404859634</v>
-      </c>
-      <c r="H88" s="80">
+        <v/>
+      </c>
+      <c r="H88" s="80" t="str">
         <f>IF(OR($B89=""),$B89,(Cáratula!$K$39/365*E88))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I88" s="79">
+        <v/>
+      </c>
+      <c r="I88" s="79" t="str">
         <f t="shared" si="4"/>
-        <v>94.552164566848717</v>
-      </c>
-      <c r="J88" s="82">
+        <v/>
+      </c>
+      <c r="J88" s="82" t="str">
         <f>IF(OR($B89=""),"",IF(C86="",Cáratula!$P$40*E88*G87,Cáratula!$P$40*E88*G88))</f>
-        <v>8.1961610454516212</v>
-      </c>
-      <c r="K88" s="82">
+        <v/>
+      </c>
+      <c r="K88" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>1541.5794134311063</v>
-      </c>
-      <c r="L88" s="82">
+        <v/>
+      </c>
+      <c r="L88" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M88" s="82">
+        <v/>
+      </c>
+      <c r="M88" s="82" t="str">
         <f>IF(OR($B89=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N88" s="76"/>
       <c r="O88" s="76"/>
-      <c r="P88" s="82">
+      <c r="P88" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B89" s="93">
+      <c r="B89" s="93" t="str">
         <f>IF($B88=Cáratula!$G$35,$B$21,IF(OR($B88="",$B88=$B$21),"",$B88+1))</f>
-        <v>67</v>
-      </c>
-      <c r="C89" s="94">
+        <v/>
+      </c>
+      <c r="C89" s="94" t="str">
         <f>IF(OR($B90=""),$B90,IF(DAY(EOMONTH($C88,1))&lt;Cáratula!$D$69,EOMONTH($C88,1),DATE(YEAR(EOMONTH($C88,1)),MONTH(EOMONTH($C88,1)),Cáratula!$D$69)))</f>
-        <v>48228</v>
-      </c>
-      <c r="D89" s="95">
+        <v/>
+      </c>
+      <c r="D89" s="95" t="str">
         <f>IF(OR($B90=""),"",$C89-Cáratula!$G$38)</f>
-        <v>2010</v>
-      </c>
-      <c r="E89" s="95">
+        <v/>
+      </c>
+      <c r="E89" s="95" t="str">
         <f>IF(OR($B90=""),"",C89-C88)</f>
-        <v>31</v>
-      </c>
-      <c r="F89" s="86">
+        <v/>
+      </c>
+      <c r="F89" s="86" t="str">
         <f t="shared" si="8"/>
-        <v>10834.415404859634</v>
-      </c>
-      <c r="G89" s="86">
+        <v/>
+      </c>
+      <c r="G89" s="86" t="str">
         <f t="shared" ref="G89:G90" si="10">IF(OR($B90=""),"",F89-K88)</f>
-        <v>9292.8359914285284</v>
-      </c>
-      <c r="H89" s="87">
+        <v/>
+      </c>
+      <c r="H89" s="87" t="str">
         <f>IF(OR($B90=""),$B90,(Cáratula!$K$39/365*E89))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I89" s="86">
+        <v/>
+      </c>
+      <c r="I89" s="86" t="str">
         <f t="shared" ref="I89:I90" si="11">IF(OR($B90=""),$B90,(H89*G89))</f>
-        <v>83.802061851795628</v>
-      </c>
-      <c r="J89" s="88">
+        <v/>
+      </c>
+      <c r="J89" s="88" t="str">
         <f>IF(OR($B90=""),"",IF(C87="",Cáratula!$P$40*E89*G88,Cáratula!$P$40*E89*G89))</f>
-        <v>7.2642990038858999</v>
-      </c>
-      <c r="K89" s="88">
+        <v/>
+      </c>
+      <c r="K89" s="88" t="str">
         <f t="shared" ref="K89:K90" si="12">IF(OR($B90=""),"",L89-I89-J89)</f>
-        <v>1553.2613781877251</v>
-      </c>
-      <c r="L89" s="88">
+        <v/>
+      </c>
+      <c r="L89" s="88" t="str">
         <f t="shared" ref="L89:L95" si="13">IF(OR($B90=""),"",L88)</f>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M89" s="88">
+        <v/>
+      </c>
+      <c r="M89" s="88" t="str">
         <f>IF(OR($B90=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N89" s="84"/>
       <c r="O89" s="84"/>
-      <c r="P89" s="88">
+      <c r="P89" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B90" s="92">
+      <c r="B90" s="92" t="str">
         <f>IF($B89=Cáratula!$G$35,$B$21,IF(OR($B89="",$B89=$B$21),"",$B89+1))</f>
-        <v>68</v>
-      </c>
-      <c r="C90" s="77">
+        <v/>
+      </c>
+      <c r="C90" s="77" t="str">
         <f>IF(OR($B91=""),$B91,IF(DAY(EOMONTH($C89,1))&lt;Cáratula!$D$69,EOMONTH($C89,1),DATE(YEAR(EOMONTH($C89,1)),MONTH(EOMONTH($C89,1)),Cáratula!$D$69)))</f>
-        <v>48259</v>
-      </c>
-      <c r="D90" s="76">
+        <v/>
+      </c>
+      <c r="D90" s="76" t="str">
         <f>IF(OR($B91=""),"",$C90-Cáratula!$G$38)</f>
-        <v>2041</v>
-      </c>
-      <c r="E90" s="76">
+        <v/>
+      </c>
+      <c r="E90" s="76" t="str">
         <f t="shared" ref="E90" si="14">IF(OR($B91=""),"",C90-C89)</f>
-        <v>31</v>
-      </c>
-      <c r="F90" s="79">
+        <v/>
+      </c>
+      <c r="F90" s="79" t="str">
         <f t="shared" ref="F90:F91" si="15">IF(OR($B91=""),"",G89)</f>
-        <v>9292.8359914285284</v>
-      </c>
-      <c r="G90" s="79">
+        <v/>
+      </c>
+      <c r="G90" s="79" t="str">
         <f t="shared" si="10"/>
-        <v>7739.574613240803</v>
-      </c>
-      <c r="H90" s="80">
+        <v/>
+      </c>
+      <c r="H90" s="80" t="str">
         <f>IF(OR($B91=""),$B91,(Cáratula!$K$39/365*E90))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I90" s="79">
+        <v/>
+      </c>
+      <c r="I90" s="79" t="str">
         <f t="shared" si="11"/>
-        <v>69.794873281271478</v>
-      </c>
-      <c r="J90" s="82">
+        <v/>
+      </c>
+      <c r="J90" s="82" t="str">
         <f>IF(OR($B91=""),"",IF(C88="",Cáratula!$P$40*E90*G89,Cáratula!$P$40*E90*G90))</f>
-        <v>6.0500996902693664</v>
-      </c>
-      <c r="K90" s="82">
+        <v/>
+      </c>
+      <c r="K90" s="82" t="str">
         <f t="shared" si="12"/>
-        <v>1568.4827660718656</v>
-      </c>
-      <c r="L90" s="82">
+        <v/>
+      </c>
+      <c r="L90" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M90" s="82">
+        <v/>
+      </c>
+      <c r="M90" s="82" t="str">
         <f>IF(OR($B91=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N90" s="76"/>
       <c r="O90" s="76"/>
-      <c r="P90" s="82">
+      <c r="P90" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B91" s="93">
+      <c r="B91" s="93" t="str">
         <f>IF($B90=Cáratula!$G$35,$B$21,IF(OR($B90="",$B90=$B$21),"",$B90+1))</f>
-        <v>69</v>
-      </c>
-      <c r="C91" s="94">
+        <v/>
+      </c>
+      <c r="C91" s="94" t="str">
         <f>IF(OR($B92=""),$B92,IF(DAY(EOMONTH($C90,1))&lt;Cáratula!$D$69,EOMONTH($C90,1),DATE(YEAR(EOMONTH($C90,1)),MONTH(EOMONTH($C90,1)),Cáratula!$D$69)))</f>
-        <v>48288</v>
-      </c>
-      <c r="D91" s="95">
+        <v/>
+      </c>
+      <c r="D91" s="95" t="str">
         <f>IF(OR($B92=""),"",$C91-Cáratula!$G$38)</f>
-        <v>2070</v>
-      </c>
-      <c r="E91" s="95">
+        <v/>
+      </c>
+      <c r="E91" s="95" t="str">
         <f>IF(OR($B92=""),"",C91-C90)</f>
-        <v>29</v>
-      </c>
-      <c r="F91" s="86">
+        <v/>
+      </c>
+      <c r="F91" s="86" t="str">
         <f t="shared" si="15"/>
-        <v>7739.574613240803</v>
-      </c>
-      <c r="G91" s="86">
+        <v/>
+      </c>
+      <c r="G91" s="86" t="str">
         <f t="shared" ref="G91" si="16">IF(OR($B92=""),"",F91-K90)</f>
-        <v>6171.0918471689374</v>
-      </c>
-      <c r="H91" s="87">
+        <v/>
+      </c>
+      <c r="H91" s="87" t="str">
         <f>IF(OR($B92=""),$B92,(Cáratula!$K$39/365*E91))</f>
-        <v>8.4361197473522467E-3</v>
-      </c>
-      <c r="I91" s="86">
+        <v/>
+      </c>
+      <c r="I91" s="86" t="str">
         <f t="shared" ref="I91" si="17">IF(OR($B92=""),$B92,(H91*G91))</f>
-        <v>52.060069794626322</v>
-      </c>
-      <c r="J91" s="88">
+        <v/>
+      </c>
+      <c r="J91" s="88" t="str">
         <f>IF(OR($B92=""),"",IF(C89="",Cáratula!$P$40*E91*G90,Cáratula!$P$40*E91*G91))</f>
-        <v>4.5127757574765592</v>
-      </c>
-      <c r="K91" s="88">
+        <v/>
+      </c>
+      <c r="K91" s="88" t="str">
         <f t="shared" ref="K91" si="18">IF(OR($B92=""),"",L91-I91-J91)</f>
-        <v>1587.7548934913038</v>
-      </c>
-      <c r="L91" s="88">
+        <v/>
+      </c>
+      <c r="L91" s="88" t="str">
         <f t="shared" si="13"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M91" s="88">
+        <v/>
+      </c>
+      <c r="M91" s="88" t="str">
         <f>IF(OR($B92=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N91" s="84"/>
       <c r="O91" s="84"/>
-      <c r="P91" s="88">
+      <c r="P91" s="88" t="str">
         <f t="shared" si="7"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B92" s="92">
+      <c r="B92" s="92" t="str">
         <f>IF($B91=Cáratula!$G$35,$B$21,IF(OR($B91="",$B91=$B$21),"",$B91+1))</f>
-        <v>70</v>
-      </c>
-      <c r="C92" s="77">
+        <v/>
+      </c>
+      <c r="C92" s="77" t="str">
         <f>IF(OR($B93=""),$B93,IF(DAY(EOMONTH($C91,1))&lt;Cáratula!$D$69,EOMONTH($C91,1),DATE(YEAR(EOMONTH($C91,1)),MONTH(EOMONTH($C91,1)),Cáratula!$D$69)))</f>
-        <v>48319</v>
-      </c>
-      <c r="D92" s="76">
+        <v/>
+      </c>
+      <c r="D92" s="76" t="str">
         <f>IF(OR($B93=""),"",$C92-Cáratula!$G$38)</f>
-        <v>2101</v>
-      </c>
-      <c r="E92" s="76">
+        <v/>
+      </c>
+      <c r="E92" s="76" t="str">
         <f>IF(OR($B93=""),"",C92-C91)</f>
-        <v>31</v>
-      </c>
-      <c r="F92" s="79">
+        <v/>
+      </c>
+      <c r="F92" s="79" t="str">
         <f t="shared" ref="F92" si="19">IF(OR($B93=""),"",G91)</f>
-        <v>6171.0918471689374</v>
-      </c>
-      <c r="G92" s="79">
+        <v/>
+      </c>
+      <c r="G92" s="79" t="str">
         <f t="shared" ref="G92" si="20">IF(OR($B93=""),"",F92-K91)</f>
-        <v>4583.3369536776336</v>
-      </c>
-      <c r="H92" s="80">
+        <v/>
+      </c>
+      <c r="H92" s="80" t="str">
         <f>IF(OR($B93=""),$B93,(Cáratula!$K$39/365*E92))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I92" s="79">
+        <v/>
+      </c>
+      <c r="I92" s="79" t="str">
         <f t="shared" ref="I92" si="21">IF(OR($B93=""),$B93,(H92*G92))</f>
-        <v>41.332171065322918</v>
-      </c>
-      <c r="J92" s="82">
+        <v/>
+      </c>
+      <c r="J92" s="82" t="str">
         <f>IF(OR($B93=""),"",IF(C90="",Cáratula!$P$40*E92*G91,Cáratula!$P$40*E92*G92))</f>
-        <v>3.5828384464962113</v>
-      </c>
-      <c r="K92" s="82">
+        <v/>
+      </c>
+      <c r="K92" s="82" t="str">
         <f t="shared" ref="K92" si="22">IF(OR($B93=""),"",L92-I92-J92)</f>
-        <v>1599.4127295315875</v>
-      </c>
-      <c r="L92" s="82">
+        <v/>
+      </c>
+      <c r="L92" s="82" t="str">
         <f t="shared" si="13"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M92" s="82">
+        <v/>
+      </c>
+      <c r="M92" s="82" t="str">
         <f>IF(OR($B93=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N92" s="76"/>
       <c r="O92" s="76"/>
-      <c r="P92" s="82">
+      <c r="P92" s="82" t="str">
         <f t="shared" ref="P92:P95" si="23">IF(OR($B93=""),"",O92+N92+M92+L92)</f>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B93" s="93">
+      <c r="B93" s="93" t="str">
         <f>IF($B92=Cáratula!$G$35,$B$21,IF(OR($B92="",$B92=$B$21),"",$B92+1))</f>
-        <v>71</v>
-      </c>
-      <c r="C93" s="94">
+        <v/>
+      </c>
+      <c r="C93" s="94" t="str">
         <f>IF(OR($B94=""),$B94,IF(DAY(EOMONTH($C92,1))&lt;Cáratula!$D$69,EOMONTH($C92,1),DATE(YEAR(EOMONTH($C92,1)),MONTH(EOMONTH($C92,1)),Cáratula!$D$69)))</f>
-        <v>48349</v>
-      </c>
-      <c r="D93" s="95">
+        <v/>
+      </c>
+      <c r="D93" s="95" t="str">
         <f>IF(OR($B94=""),"",$C93-Cáratula!$G$38)</f>
-        <v>2131</v>
-      </c>
-      <c r="E93" s="95">
+        <v/>
+      </c>
+      <c r="E93" s="95" t="str">
         <f>IF(OR($B94=""),"",C93-C92)</f>
-        <v>30</v>
-      </c>
-      <c r="F93" s="86">
+        <v/>
+      </c>
+      <c r="F93" s="86" t="str">
         <f t="shared" ref="F93:F94" si="24">IF(OR($B94=""),"",G92)</f>
-        <v>4583.3369536776336</v>
-      </c>
-      <c r="G93" s="86">
+        <v/>
+      </c>
+      <c r="G93" s="86" t="str">
         <f t="shared" ref="G93:G94" si="25">IF(OR($B94=""),"",F93-K92)</f>
-        <v>2983.9242241460461</v>
-      </c>
-      <c r="H93" s="87">
+        <v/>
+      </c>
+      <c r="H93" s="87" t="str">
         <f>IF(OR($B94=""),$B94,(Cáratula!$K$39/365*E93))</f>
-        <v>8.7270204282954289E-3</v>
-      </c>
-      <c r="I93" s="86">
+        <v/>
+      </c>
+      <c r="I93" s="86" t="str">
         <f t="shared" ref="I93:I94" si="26">IF(OR($B94=""),$B94,(H93*G93))</f>
-        <v>26.040767660608132</v>
-      </c>
-      <c r="J93" s="88">
+        <v/>
+      </c>
+      <c r="J93" s="88" t="str">
         <f>IF(OR($B94=""),"",IF(C91="",Cáratula!$P$40*E93*G92,Cáratula!$P$40*E93*G93))</f>
-        <v>2.2573182377293319</v>
-      </c>
-      <c r="K93" s="88">
+        <v/>
+      </c>
+      <c r="K93" s="88" t="str">
         <f t="shared" ref="K93:K94" si="27">IF(OR($B94=""),"",L93-I93-J93)</f>
-        <v>1616.0296531450692</v>
-      </c>
-      <c r="L93" s="88">
+        <v/>
+      </c>
+      <c r="L93" s="88" t="str">
         <f t="shared" si="13"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M93" s="88">
+        <v/>
+      </c>
+      <c r="M93" s="88" t="str">
         <f>IF(OR($B94=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N93" s="84"/>
       <c r="O93" s="84"/>
-      <c r="P93" s="88">
+      <c r="P93" s="88" t="str">
         <f t="shared" si="23"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B94" s="92">
+      <c r="B94" s="92" t="str">
         <f>IF($B93=Cáratula!$G$35,$B$21,IF(OR($B93="",$B93=$B$21),"",$B93+1))</f>
-        <v>72</v>
-      </c>
-      <c r="C94" s="77">
+        <v/>
+      </c>
+      <c r="C94" s="77" t="str">
         <f>IF(OR($B95=""),$B95,IF(DAY(EOMONTH($C93,1))&lt;Cáratula!$D$69,EOMONTH($C93,1),DATE(YEAR(EOMONTH($C93,1)),MONTH(EOMONTH($C93,1)),Cáratula!$D$69)))</f>
-        <v>48380</v>
-      </c>
-      <c r="D94" s="76">
+        <v/>
+      </c>
+      <c r="D94" s="76" t="str">
         <f>IF(OR($B95=""),"",$C94-Cáratula!$G$38)</f>
-        <v>2162</v>
-      </c>
-      <c r="E94" s="76">
+        <v/>
+      </c>
+      <c r="E94" s="76" t="str">
         <f>IF(OR($B95=""),"",C94-C93)</f>
-        <v>31</v>
-      </c>
-      <c r="F94" s="79">
+        <v/>
+      </c>
+      <c r="F94" s="79" t="str">
         <f t="shared" si="24"/>
-        <v>2983.9242241460461</v>
-      </c>
-      <c r="G94" s="79">
+        <v/>
+      </c>
+      <c r="G94" s="79" t="str">
         <f t="shared" si="25"/>
-        <v>1367.8945710009768</v>
-      </c>
-      <c r="H94" s="80">
+        <v/>
+      </c>
+      <c r="H94" s="80" t="str">
         <f>IF(OR($B95=""),$B95,(Cáratula!$K$39/365*E94))</f>
-        <v>9.0179211092386094E-3</v>
-      </c>
-      <c r="I94" s="79">
+        <v/>
+      </c>
+      <c r="I94" s="79" t="str">
         <f t="shared" si="26"/>
-        <v>12.3355653270426</v>
-      </c>
-      <c r="J94" s="82">
+        <v/>
+      </c>
+      <c r="J94" s="82" t="str">
         <f>IF(OR($B95=""),"",IF(C92="",Cáratula!$P$40*E94*G93,Cáratula!$P$40*E94*G94))</f>
-        <v>1.0692963029487197</v>
-      </c>
-      <c r="K94" s="82">
+        <v/>
+      </c>
+      <c r="K94" s="82" t="str">
         <f t="shared" si="27"/>
-        <v>1630.9228774134153</v>
-      </c>
-      <c r="L94" s="82">
+        <v/>
+      </c>
+      <c r="L94" s="82" t="str">
         <f t="shared" si="13"/>
-        <v>1644.3277390434066</v>
-      </c>
-      <c r="M94" s="82">
+        <v/>
+      </c>
+      <c r="M94" s="82" t="str">
         <f>IF(OR($B95=""),"",IF(Cáratula!$G$40="Físico",10,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N94" s="76"/>
       <c r="O94" s="76"/>
-      <c r="P94" s="82">
+      <c r="P94" s="82" t="str">
         <f t="shared" si="23"/>
-        <v>1644.3277390434066</v>
+        <v/>
       </c>
     </row>
     <row r="95" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B95" s="61">
+      <c r="B95" s="61" t="str">
         <f>IF($B94=Cáratula!$G$35,$B$21,IF(OR($B94="",$B94=$B$21),"",$B94+1))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C95" s="96" t="str">
         <f>IF(OR($B96=""),$B96,IF(DAY(EOMONTH($C94,1))&lt;Cáratula!$D$69,EOMONTH($C94,1),DATE(YEAR(EOMONTH($C94,1)),MONTH(EOMONTH($C94,1)),Cáratula!$D$69)))</f>
